--- a/Analysis/04_Robust_Core_and_Policy/3_input_eipi_results.xlsx
+++ b/Analysis/04_Robust_Core_and_Policy/3_input_eipi_results.xlsx
@@ -570,16 +570,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7943411013128591</v>
+        <v>0.7955071868527118</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6699824911239818</v>
+        <v>0.6755088414545456</v>
       </c>
       <c r="E2" t="n">
-        <v>0.868574248209378</v>
+        <v>0.8461810836006346</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9401762554595198</v>
+        <v>0.96035651629466</v>
       </c>
       <c r="G2" t="n">
         <v>0.6948302469776479</v>
@@ -588,10 +588,10 @@
         <v>0.970900284109632</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5990786900588778</v>
+        <v>0.650794257218719</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9241259782121449</v>
+        <v>0.9241259782121448</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
@@ -612,10 +612,10 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9838709677419355</v>
+        <v>0.967741935483871</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
@@ -624,25 +624,25 @@
         <v>0.9838709677419355</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9904446051399636</v>
+        <v>1</v>
       </c>
       <c r="V2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9003539144670568</v>
+        <v>0.9266532090109549</v>
       </c>
       <c r="X2" t="n">
         <v>2</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.8423614871417641</v>
+        <v>0.8097003993816735</v>
       </c>
       <c r="Z2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.8995212246499882</v>
+        <v>0.9178489733153056</v>
       </c>
       <c r="AB2" t="n">
         <v>2</v>
@@ -655,31 +655,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01359138848836977</v>
+        <v>0.01304944363710139</v>
       </c>
       <c r="C3" t="n">
-        <v>0.09821008000298369</v>
+        <v>0.09820965725143535</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4080702528623372</v>
+        <v>0.3908737599714858</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1005802595370544</v>
+        <v>0.04349053927557237</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0195546957487966</v>
+        <v>0.02035518867264613</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04239782507949156</v>
+        <v>0.04239782507949155</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06089013334697348</v>
+        <v>0.06089013334697349</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3862968150312398</v>
+        <v>0.3339914434384297</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4703905347546599</v>
+        <v>0.47039053475466</v>
       </c>
       <c r="K3" t="n">
         <v>50</v>
@@ -694,16 +694,16 @@
         <v>0.2258064516129032</v>
       </c>
       <c r="O3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6290322580645161</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="Q3" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4032258064516129</v>
+        <v>0.3225806451612903</v>
       </c>
       <c r="S3" t="n">
         <v>46</v>
@@ -712,25 +712,25 @@
         <v>0.2741935483870968</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4356857864518975</v>
+        <v>0.4249839345544715</v>
       </c>
       <c r="V3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4717221431873859</v>
+        <v>0.4777217108720155</v>
       </c>
       <c r="X3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.4496672482920687</v>
+      </c>
+      <c r="Z3" t="n">
         <v>9</v>
       </c>
-      <c r="Y3" t="n">
-        <v>0.4391764224335984</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>10</v>
-      </c>
       <c r="AA3" t="n">
-        <v>0.4167485892118711</v>
+        <v>0.4298902597192675</v>
       </c>
       <c r="AB3" t="n">
         <v>10</v>
@@ -743,82 +743,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003692339699757447</v>
+        <v>0.005337086976234392</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0929933070463259</v>
+        <v>0.09407307885677467</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4033827483259416</v>
+        <v>0.3888784024991742</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07039871614177998</v>
+        <v>0.008841203565555001</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002106996705871131</v>
+        <v>0.00309866894974924</v>
       </c>
       <c r="G4" t="n">
         <v>0.01028019879276019</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05030183092567807</v>
+        <v>0.05030183092567809</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4057193439968776</v>
+        <v>0.3575518950083084</v>
       </c>
       <c r="J4" t="n">
         <v>0.4713053314122678</v>
       </c>
       <c r="K4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.04838709677419355</v>
+      </c>
+      <c r="M4" t="n">
+        <v>60</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.04838709677419355</v>
+      </c>
+      <c r="O4" t="n">
+        <v>28</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.5645161290322581</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>60</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.04838709677419355</v>
+      </c>
+      <c r="S4" t="n">
         <v>61</v>
       </c>
-      <c r="L4" t="n">
+      <c r="T4" t="n">
         <v>0.03225806451612903</v>
       </c>
-      <c r="M4" t="n">
-        <v>61</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.03225806451612903</v>
-      </c>
-      <c r="O4" t="n">
-        <v>34</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.4677419354838709</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>58</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.08064516129032258</v>
-      </c>
-      <c r="S4" t="n">
-        <v>60</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.04838709677419355</v>
-      </c>
       <c r="U4" t="n">
-        <v>0.4267791127204308</v>
+        <v>0.4184397474306021</v>
       </c>
       <c r="V4" t="n">
         <v>14</v>
       </c>
       <c r="W4" t="n">
-        <v>0.465963475536688</v>
+        <v>0.4735609359520173</v>
       </c>
       <c r="X4" t="n">
         <v>12</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4098965625425127</v>
+        <v>0.4153782909205798</v>
       </c>
       <c r="Z4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.3994197104505816</v>
+        <v>0.4124154715678632</v>
       </c>
       <c r="AB4" t="n">
         <v>13</v>
@@ -831,19 +831,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05690451593893761</v>
+        <v>0.05887950811108643</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1750160553431322</v>
+        <v>0.1750780989899745</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3946762912514155</v>
+        <v>0.3797469398020965</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1335580279544446</v>
+        <v>0.1092456405486102</v>
       </c>
       <c r="F5" t="n">
-        <v>0.07898058283467432</v>
+        <v>0.0937416529208303</v>
       </c>
       <c r="G5" t="n">
         <v>0.2060184721967299</v>
@@ -852,16 +852,16 @@
         <v>0.1263193957937011</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3792998473918334</v>
+        <v>0.3374553807745517</v>
       </c>
       <c r="J5" t="n">
         <v>0.3462110528959643</v>
       </c>
       <c r="K5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5483870967741935</v>
+        <v>0.5645161290322581</v>
       </c>
       <c r="M5" t="n">
         <v>24</v>
@@ -876,37 +876,37 @@
         <v>0.2096774193548387</v>
       </c>
       <c r="Q5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6290322580645161</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5645161290322581</v>
+        <v>0.5483870967741935</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1780530787239071</v>
+        <v>0.1846218812499254</v>
       </c>
       <c r="V5" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2025742547036805</v>
+        <v>0.2064945890433726</v>
       </c>
       <c r="X5" t="n">
         <v>43</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.2561234574211091</v>
+        <v>0.2455622051035936</v>
       </c>
       <c r="Z5" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1740608658788663</v>
+        <v>0.1791144047537774</v>
       </c>
       <c r="AB5" t="n">
         <v>43</v>
@@ -919,19 +919,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6645935384140625</v>
+        <v>0.6373912342094957</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5334558547428119</v>
+        <v>0.5302723124022803</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5336889017514732</v>
+        <v>0.5155984222806251</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5269947283956284</v>
+        <v>0.5040611883394027</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5850232070167459</v>
+        <v>0.5936575968281768</v>
       </c>
       <c r="G6" t="n">
         <v>0.4962382519789826</v>
@@ -940,10 +940,10 @@
         <v>0.5550456384326018</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4631125240633031</v>
+        <v>0.4155921123262515</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9166302048269644</v>
+        <v>0.9166302048269642</v>
       </c>
       <c r="K6" t="n">
         <v>7</v>
@@ -958,10 +958,10 @@
         <v>0.9032258064516129</v>
       </c>
       <c r="O6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9354838709677419</v>
+        <v>0.9516129032258065</v>
       </c>
       <c r="Q6" t="n">
         <v>7</v>
@@ -976,25 +976,25 @@
         <v>0.9032258064516129</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6079501653753897</v>
+        <v>0.5903679542265067</v>
       </c>
       <c r="V6" t="n">
         <v>7</v>
       </c>
       <c r="W6" t="n">
-        <v>0.4671588285817264</v>
+        <v>0.4758145086530895</v>
       </c>
       <c r="X6" t="n">
         <v>11</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4859348661744049</v>
+        <v>0.4422044593446146</v>
       </c>
       <c r="Z6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.4927195001585572</v>
+        <v>0.4859496108351066</v>
       </c>
       <c r="AB6" t="n">
         <v>8</v>
@@ -1007,31 +1007,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4866306598104315</v>
+        <v>0.4817229697174627</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4155447567376714</v>
+        <v>0.4158416312567653</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5054084881436636</v>
+        <v>0.5155586252705225</v>
       </c>
       <c r="E7" t="n">
-        <v>0.358153304136632</v>
+        <v>0.3458329291081266</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4100789003686539</v>
+        <v>0.4317961884136103</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3231840806718937</v>
+        <v>0.3231840806718938</v>
       </c>
       <c r="H7" t="n">
         <v>0.46135383012658</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5257615608210163</v>
+        <v>0.5124059589531199</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7185894190665461</v>
+        <v>0.7185894190665459</v>
       </c>
       <c r="K7" t="n">
         <v>8</v>
@@ -1046,10 +1046,10 @@
         <v>0.8709677419354839</v>
       </c>
       <c r="O7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8870967741935484</v>
+        <v>0.9354838709677419</v>
       </c>
       <c r="Q7" t="n">
         <v>8</v>
@@ -1064,25 +1064,25 @@
         <v>0.8870967741935484</v>
       </c>
       <c r="U7" t="n">
-        <v>0.452172605952452</v>
+        <v>0.4581891321377697</v>
       </c>
       <c r="V7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3306373351054986</v>
+        <v>0.3410294620660286</v>
       </c>
       <c r="X7" t="n">
         <v>23</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3428857956039999</v>
+        <v>0.3135771224997562</v>
       </c>
       <c r="Z7" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.3395195653839166</v>
+        <v>0.3457391360966371</v>
       </c>
       <c r="AB7" t="n">
         <v>19</v>
@@ -1095,28 +1095,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01065921917711803</v>
+        <v>0.009644249733570186</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1019290159703303</v>
+        <v>0.1017142677291686</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3988100423928895</v>
+        <v>0.3816901746981674</v>
       </c>
       <c r="E8" t="n">
-        <v>0.09175929246617026</v>
+        <v>0.04246496474679754</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01663097036620498</v>
+        <v>0.02030931901203929</v>
       </c>
       <c r="G8" t="n">
-        <v>0.07313638328756222</v>
+        <v>0.0731363832875622</v>
       </c>
       <c r="H8" t="n">
-        <v>0.05730270571636061</v>
+        <v>0.05730270571636062</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3839032218227507</v>
+        <v>0.3301743001695824</v>
       </c>
       <c r="J8" t="n">
         <v>0.4390072565795425</v>
@@ -1140,37 +1140,37 @@
         <v>0.3064516129032258</v>
       </c>
       <c r="Q8" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3225806451612903</v>
+        <v>0.3064516129032258</v>
       </c>
       <c r="S8" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2419354838709677</v>
+        <v>0.2580645161290323</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2298714811555191</v>
+        <v>0.2284728763831992</v>
       </c>
       <c r="V8" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2176883363946372</v>
+        <v>0.2200244751533915</v>
       </c>
       <c r="X8" t="n">
         <v>41</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.2865247594750786</v>
+        <v>0.2677901352061005</v>
       </c>
       <c r="Z8" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.2087831131748076</v>
+        <v>0.2079859570018951</v>
       </c>
       <c r="AB8" t="n">
         <v>36</v>
@@ -1183,19 +1183,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.04013598895879208</v>
+        <v>0.03884265227640725</v>
       </c>
       <c r="C9" t="n">
-        <v>0.115293024446433</v>
+        <v>0.1153920393998452</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4041800554079524</v>
+        <v>0.3880874918955128</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1115324034752138</v>
+        <v>0.0634057663778109</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03977267354858268</v>
+        <v>0.04407938236204837</v>
       </c>
       <c r="G9" t="n">
         <v>0.08663989889557584</v>
@@ -1204,16 +1204,16 @@
         <v>0.07712647595589892</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3910593835512647</v>
+        <v>0.3397426172447696</v>
       </c>
       <c r="J9" t="n">
         <v>0.4651316394675757</v>
       </c>
       <c r="K9" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4193548387096774</v>
+        <v>0.4032258064516129</v>
       </c>
       <c r="M9" t="n">
         <v>37</v>
@@ -1222,46 +1222,46 @@
         <v>0.4193548387096774</v>
       </c>
       <c r="O9" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5161290322580645</v>
+        <v>0.532258064516129</v>
       </c>
       <c r="Q9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4677419354838709</v>
+        <v>0.4516129032258064</v>
       </c>
       <c r="S9" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4193548387096774</v>
+        <v>0.4354838709677419</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1968516465199397</v>
+        <v>0.1981355867772255</v>
       </c>
       <c r="V9" t="n">
         <v>44</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1549545931184198</v>
+        <v>0.1572135567635841</v>
       </c>
       <c r="X9" t="n">
         <v>49</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.2601646090048121</v>
+        <v>0.2311094842536609</v>
       </c>
       <c r="Z9" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.1682395624504765</v>
+        <v>0.1633256330085542</v>
       </c>
       <c r="AB9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10">
@@ -1271,37 +1271,37 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.008228186003674072</v>
+        <v>0.007861488661276053</v>
       </c>
       <c r="C10" t="n">
-        <v>0.09520297839764717</v>
+        <v>0.09527259888857649</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4028120668531125</v>
+        <v>0.385898732373005</v>
       </c>
       <c r="E10" t="n">
-        <v>0.08702510520018039</v>
+        <v>0.02954143984997901</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01113976039104596</v>
+        <v>0.01213602944219254</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0376717138365299</v>
+        <v>0.03767171383652988</v>
       </c>
       <c r="H10" t="n">
-        <v>0.05481428045548185</v>
+        <v>0.05481428045548187</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3885109518447517</v>
+        <v>0.3360612281306767</v>
       </c>
       <c r="J10" t="n">
         <v>0.4668592837474414</v>
       </c>
       <c r="K10" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L10" t="n">
-        <v>0.08064516129032258</v>
+        <v>0.06451612903225806</v>
       </c>
       <c r="M10" t="n">
         <v>55</v>
@@ -1310,10 +1310,10 @@
         <v>0.1290322580645161</v>
       </c>
       <c r="O10" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4032258064516129</v>
+        <v>0.4516129032258064</v>
       </c>
       <c r="Q10" t="n">
         <v>49</v>
@@ -1322,34 +1322,34 @@
         <v>0.2258064516129032</v>
       </c>
       <c r="S10" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1290322580645161</v>
+        <v>0.1451612903225807</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3491353097578615</v>
+        <v>0.3425613430432314</v>
       </c>
       <c r="V10" t="n">
         <v>23</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3634324005243063</v>
+        <v>0.3680510479617638</v>
       </c>
       <c r="X10" t="n">
         <v>19</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.3681961496538981</v>
+        <v>0.3631711620862867</v>
       </c>
       <c r="Z10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.3259233378033231</v>
+        <v>0.3322118846610039</v>
       </c>
       <c r="AB10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
@@ -1359,19 +1359,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.05595741524671614</v>
+        <v>0.05361837605909077</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1298884732911294</v>
+        <v>0.1296987412368753</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4053300195950734</v>
+        <v>0.3906993291624234</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1281316887090916</v>
+        <v>0.08799962768761775</v>
       </c>
       <c r="F11" t="n">
-        <v>0.05767474045235919</v>
+        <v>0.06446689432207309</v>
       </c>
       <c r="G11" t="n">
         <v>0.1132731117203565</v>
@@ -1380,7 +1380,7 @@
         <v>0.09305005881621876</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3853898731169649</v>
+        <v>0.3332491349556314</v>
       </c>
       <c r="J11" t="n">
         <v>0.4639955877369914</v>
@@ -1398,46 +1398,46 @@
         <v>0.4838709677419355</v>
       </c>
       <c r="O11" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5645161290322581</v>
+        <v>0.5967741935483871</v>
       </c>
       <c r="Q11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5483870967741935</v>
+        <v>0.532258064516129</v>
       </c>
       <c r="S11" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4677419354838709</v>
+        <v>0.4838709677419355</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1326242266161869</v>
+        <v>0.1366155674761129</v>
       </c>
       <c r="V11" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="W11" t="n">
-        <v>0.07346825434695867</v>
+        <v>0.07443593214077106</v>
       </c>
       <c r="X11" t="n">
         <v>61</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.2191238206474832</v>
+        <v>0.1838220278676475</v>
       </c>
       <c r="Z11" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.1055645865331218</v>
+        <v>0.09712575380623777</v>
       </c>
       <c r="AB11" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12">
@@ -1447,28 +1447,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0910753681870128</v>
+        <v>0.09111901646559932</v>
       </c>
       <c r="C12" t="n">
-        <v>0.171162189538755</v>
+        <v>0.1716182088232219</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4176134794736873</v>
+        <v>0.4093568192229806</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1554100609123282</v>
+        <v>0.1328534073137473</v>
       </c>
       <c r="F12" t="n">
-        <v>0.09730745857002301</v>
+        <v>0.1121476263675645</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1689873106146918</v>
+        <v>0.1689873106146917</v>
       </c>
       <c r="H12" t="n">
         <v>0.1374727300833208</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4101244691267755</v>
+        <v>0.367273720714394</v>
       </c>
       <c r="J12" t="n">
         <v>0.4184791754952872</v>
@@ -1486,16 +1486,16 @@
         <v>0.6129032258064516</v>
       </c>
       <c r="O12" t="n">
+        <v>16</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.7580645161290323</v>
+      </c>
+      <c r="Q12" t="n">
         <v>18</v>
       </c>
-      <c r="P12" t="n">
+      <c r="R12" t="n">
         <v>0.7258064516129032</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>19</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.7096774193548387</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1504,25 +1504,25 @@
         <v>0.6935483870967742</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1494065809172398</v>
+        <v>0.1568547508210429</v>
       </c>
       <c r="V12" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1112822979256792</v>
+        <v>0.1145631161510657</v>
       </c>
       <c r="X12" t="n">
         <v>56</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.2313081536785767</v>
+        <v>0.2109413630750346</v>
       </c>
       <c r="Z12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.1273618139278035</v>
+        <v>0.1274568993159804</v>
       </c>
       <c r="AB12" t="n">
         <v>51</v>
@@ -1535,37 +1535,37 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.01750618203003422</v>
+        <v>0.01515595000127943</v>
       </c>
       <c r="C13" t="n">
-        <v>0.09975380923602793</v>
+        <v>0.09926778697791151</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4031956842687456</v>
+        <v>0.3855614710935187</v>
       </c>
       <c r="E13" t="n">
-        <v>0.09866557889692364</v>
+        <v>0.04487262935461288</v>
       </c>
       <c r="F13" t="n">
-        <v>0.02072396151691537</v>
+        <v>0.02205338292153482</v>
       </c>
       <c r="G13" t="n">
         <v>0.05517392021183942</v>
       </c>
       <c r="H13" t="n">
-        <v>0.05852406836282899</v>
+        <v>0.058524068362829</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3833797056275062</v>
+        <v>0.3272076023922347</v>
       </c>
       <c r="J13" t="n">
         <v>0.471743763247589</v>
       </c>
       <c r="K13" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2741935483870968</v>
+        <v>0.2580645161290323</v>
       </c>
       <c r="M13" t="n">
         <v>47</v>
@@ -1574,16 +1574,16 @@
         <v>0.2580645161290323</v>
       </c>
       <c r="O13" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P13" t="n">
-        <v>0.4516129032258064</v>
+        <v>0.4354838709677419</v>
       </c>
       <c r="Q13" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="R13" t="n">
-        <v>0.3870967741935484</v>
+        <v>0.3387096774193548</v>
       </c>
       <c r="S13" t="n">
         <v>45</v>
@@ -1592,25 +1592,25 @@
         <v>0.2903225806451613</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2938478120558171</v>
+        <v>0.2882115283869602</v>
       </c>
       <c r="V13" t="n">
         <v>27</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2866225631433422</v>
+        <v>0.2893918768172526</v>
       </c>
       <c r="X13" t="n">
         <v>28</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.3335694404835768</v>
+        <v>0.3206580608778492</v>
       </c>
       <c r="Z13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.2703458127691244</v>
+        <v>0.271766911075668</v>
       </c>
       <c r="AB13" t="n">
         <v>28</v>
@@ -1623,28 +1623,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.08178405566220211</v>
+        <v>0.0773353276572159</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1702016232154539</v>
+        <v>0.1694567353350122</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3927059999735275</v>
+        <v>0.3786767419153148</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1334573857656136</v>
+        <v>0.1140405126497557</v>
       </c>
       <c r="F14" t="n">
-        <v>0.08511191475993481</v>
+        <v>0.09948580121651855</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2082409240535935</v>
+        <v>0.2082409240535934</v>
       </c>
       <c r="H14" t="n">
         <v>0.1060887383607155</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3846182594795103</v>
+        <v>0.3301805674022597</v>
       </c>
       <c r="J14" t="n">
         <v>0.4151204449424001</v>
@@ -1662,46 +1662,46 @@
         <v>0.5967741935483871</v>
       </c>
       <c r="O14" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1612903225806452</v>
+        <v>0.1935483870967742</v>
       </c>
       <c r="Q14" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="R14" t="n">
-        <v>0.5967741935483871</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="S14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6290322580645161</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1424196174441631</v>
+        <v>0.144840916178343</v>
       </c>
       <c r="V14" t="n">
         <v>54</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1139314846983473</v>
+        <v>0.1152627155268247</v>
       </c>
       <c r="X14" t="n">
         <v>55</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.2112864108949263</v>
+        <v>0.1942598219197131</v>
       </c>
       <c r="Z14" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.1171238390409153</v>
+        <v>0.1165897155826835</v>
       </c>
       <c r="AB14" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15">
@@ -1711,37 +1711,37 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05452034053675623</v>
+        <v>0.04926738230900282</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1874626549735211</v>
+        <v>0.1860422676952249</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3833272621059462</v>
+        <v>0.3635077197213231</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1329374098387865</v>
+        <v>0.1196932986457304</v>
       </c>
       <c r="F15" t="n">
-        <v>0.08314419289928035</v>
+        <v>0.09900173556643403</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2632853979479301</v>
+        <v>0.2632853979479302</v>
       </c>
       <c r="H15" t="n">
-        <v>0.09785147264274616</v>
+        <v>0.09785147264274617</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3580062578211431</v>
+        <v>0.2988278385833515</v>
       </c>
       <c r="J15" t="n">
         <v>0.3333181855367324</v>
       </c>
       <c r="K15" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5</v>
+        <v>0.4677419354838709</v>
       </c>
       <c r="M15" t="n">
         <v>20</v>
@@ -1750,16 +1750,16 @@
         <v>0.6935483870967742</v>
       </c>
       <c r="O15" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="P15" t="n">
-        <v>0.08064516129032258</v>
+        <v>0.1129032258064516</v>
       </c>
       <c r="Q15" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="R15" t="n">
-        <v>0.5806451612903226</v>
+        <v>0.6612903225806451</v>
       </c>
       <c r="S15" t="n">
         <v>26</v>
@@ -1768,25 +1768,25 @@
         <v>0.5967741935483871</v>
       </c>
       <c r="U15" t="n">
-        <v>0.09921013655052739</v>
+        <v>0.1015550045296841</v>
       </c>
       <c r="V15" t="n">
         <v>58</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1246651895106109</v>
+        <v>0.125347178637057</v>
       </c>
       <c r="X15" t="n">
         <v>53</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.2014387994606225</v>
+        <v>0.1884198314723715</v>
       </c>
       <c r="Z15" t="n">
         <v>55</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.1016625111292161</v>
+        <v>0.1016489023672338</v>
       </c>
       <c r="AB15" t="n">
         <v>56</v>
@@ -1799,28 +1799,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.04931315008062453</v>
+        <v>0.04684644778342291</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1845131168038134</v>
+        <v>0.1837217799279185</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3953467503642544</v>
+        <v>0.3847631703172451</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1240146326110782</v>
+        <v>0.126367942741988</v>
       </c>
       <c r="F16" t="n">
-        <v>0.07664876857735707</v>
+        <v>0.09962401006529366</v>
       </c>
       <c r="G16" t="n">
         <v>0.2532668460912194</v>
       </c>
       <c r="H16" t="n">
-        <v>0.09224229137825171</v>
+        <v>0.09224229137825173</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3944780169433278</v>
+        <v>0.3413434685076035</v>
       </c>
       <c r="J16" t="n">
         <v>0.3007076172156397</v>
@@ -1838,28 +1838,28 @@
         <v>0.6774193548387096</v>
       </c>
       <c r="O16" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2258064516129032</v>
+        <v>0.4032258064516129</v>
       </c>
       <c r="Q16" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5161290322580645</v>
+        <v>0.6935483870967742</v>
       </c>
       <c r="S16" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5483870967741935</v>
+        <v>0.6290322580645161</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>0.009956328699082067</v>
       </c>
       <c r="V16" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
@@ -1868,7 +1868,7 @@
         <v>62</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.126070743573698</v>
+        <v>0.1119488757171484</v>
       </c>
       <c r="Z16" t="n">
         <v>60</v>
@@ -1887,19 +1887,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.07372145414203261</v>
+        <v>0.06711987957455187</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2064635730884081</v>
+        <v>0.2049014643533581</v>
       </c>
       <c r="D17" t="n">
-        <v>0.384803573447356</v>
+        <v>0.3702721665854359</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1354580972057984</v>
+        <v>0.1419416636289282</v>
       </c>
       <c r="F17" t="n">
-        <v>0.09839137590010592</v>
+        <v>0.1215572619088</v>
       </c>
       <c r="G17" t="n">
         <v>0.3048170334419157</v>
@@ -1908,7 +1908,7 @@
         <v>0.09081558628631627</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3751482930962308</v>
+        <v>0.3147818789593368</v>
       </c>
       <c r="J17" t="n">
         <v>0.3250686193452484</v>
@@ -1926,16 +1926,16 @@
         <v>0.7258064516129032</v>
       </c>
       <c r="O17" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="P17" t="n">
-        <v>0.09677419354838709</v>
+        <v>0.1290322580645161</v>
       </c>
       <c r="Q17" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6451612903225806</v>
+        <v>0.7419354838709677</v>
       </c>
       <c r="S17" t="n">
         <v>19</v>
@@ -1944,25 +1944,25 @@
         <v>0.7096774193548387</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0836463505619668</v>
+        <v>0.08617070901936748</v>
       </c>
       <c r="V17" t="n">
         <v>59</v>
       </c>
       <c r="W17" t="n">
-        <v>0.107890077031188</v>
+        <v>0.1084629447824246</v>
       </c>
       <c r="X17" t="n">
         <v>57</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.1779447865889229</v>
+        <v>0.1787964954211494</v>
       </c>
       <c r="Z17" t="n">
         <v>57</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.0814522838012262</v>
+        <v>0.08713203808469124</v>
       </c>
       <c r="AB17" t="n">
         <v>59</v>
@@ -1975,37 +1975,37 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.02488923374655185</v>
+        <v>0.02114450026148435</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1068020708773007</v>
+        <v>0.1059161956895492</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3976043707532602</v>
+        <v>0.3803489113946373</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1028577455271264</v>
+        <v>0.05603132749764896</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0277621584028495</v>
+        <v>0.03112329632239591</v>
       </c>
       <c r="G18" t="n">
-        <v>0.08064035111341991</v>
+        <v>0.0806403511134199</v>
       </c>
       <c r="H18" t="n">
-        <v>0.06237215753166858</v>
+        <v>0.0623721575316686</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3756911816367574</v>
+        <v>0.3169917029485306</v>
       </c>
       <c r="J18" t="n">
         <v>0.4668010421903802</v>
       </c>
       <c r="K18" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3548387096774194</v>
+        <v>0.3225806451612903</v>
       </c>
       <c r="M18" t="n">
         <v>45</v>
@@ -2014,46 +2014,46 @@
         <v>0.2903225806451613</v>
       </c>
       <c r="O18" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2580645161290323</v>
+        <v>0.2258064516129032</v>
       </c>
       <c r="Q18" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4354838709677419</v>
+        <v>0.4032258064516129</v>
       </c>
       <c r="S18" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3548387096774194</v>
+        <v>0.3225806451612903</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2323095089965548</v>
+        <v>0.228470072656473</v>
       </c>
       <c r="V18" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2084657093051238</v>
+        <v>0.2096684923385136</v>
       </c>
       <c r="X18" t="n">
         <v>42</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.2884139050493291</v>
+        <v>0.2700860544678855</v>
       </c>
       <c r="Z18" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.2077382560041582</v>
+        <v>0.2057990071576669</v>
       </c>
       <c r="AB18" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -2063,19 +2063,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.09890127487297895</v>
+        <v>0.09328927477646995</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1691241462754319</v>
+        <v>0.1682733715718762</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4078626251961849</v>
+        <v>0.3967886765261038</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1467592194864612</v>
+        <v>0.1311497885579997</v>
       </c>
       <c r="F19" t="n">
-        <v>0.09558616264079269</v>
+        <v>0.1108263905691285</v>
       </c>
       <c r="G19" t="n">
         <v>0.1911631376720676</v>
@@ -2084,16 +2084,16 @@
         <v>0.1093392642984093</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4026277660476996</v>
+        <v>0.3472231518486408</v>
       </c>
       <c r="J19" t="n">
         <v>0.4496174992859345</v>
       </c>
       <c r="K19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6774193548387096</v>
+        <v>0.6612903225806451</v>
       </c>
       <c r="M19" t="n">
         <v>28</v>
@@ -2102,46 +2102,46 @@
         <v>0.5645161290322581</v>
       </c>
       <c r="O19" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6129032258064516</v>
+        <v>0.6774193548387096</v>
       </c>
       <c r="Q19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6935483870967742</v>
+        <v>0.7096774193548387</v>
       </c>
       <c r="S19" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6451612903225806</v>
+        <v>0.6774193548387096</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1490209874277699</v>
+        <v>0.1506541191950277</v>
       </c>
       <c r="V19" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="W19" t="n">
-        <v>0.09645193403612703</v>
+        <v>0.09735748868659788</v>
       </c>
       <c r="X19" t="n">
         <v>58</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.2161115274999627</v>
+        <v>0.2011190712449819</v>
       </c>
       <c r="Z19" t="n">
         <v>52</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.1163392164179994</v>
+        <v>0.1160752799133716</v>
       </c>
       <c r="AB19" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20">
@@ -2151,31 +2151,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.05427734688590912</v>
+        <v>0.04966376002479041</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1636414274778696</v>
+        <v>0.1625741454049356</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3919597368767808</v>
+        <v>0.3811068474238026</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1021335989324989</v>
+        <v>0.0982164350980977</v>
       </c>
       <c r="F20" t="n">
-        <v>0.06085916786742904</v>
+        <v>0.08107035484025241</v>
       </c>
       <c r="G20" t="n">
         <v>0.2226161127125235</v>
       </c>
       <c r="H20" t="n">
-        <v>0.05753360691013105</v>
+        <v>0.05753360691013107</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4023622141551334</v>
+        <v>0.3446698493895909</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3694002942288727</v>
+        <v>0.3694002942288728</v>
       </c>
       <c r="K20" t="n">
         <v>33</v>
@@ -2190,43 +2190,43 @@
         <v>0.5483870967741935</v>
       </c>
       <c r="O20" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1451612903225807</v>
+        <v>0.2741935483870968</v>
       </c>
       <c r="Q20" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4193548387096774</v>
+        <v>0.5645161290322581</v>
       </c>
       <c r="S20" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5</v>
+        <v>0.5161290322580645</v>
       </c>
       <c r="U20" t="n">
-        <v>0.100951623676353</v>
+        <v>0.1039019712316544</v>
       </c>
       <c r="V20" t="n">
         <v>57</v>
       </c>
       <c r="W20" t="n">
-        <v>0.08916081431744539</v>
+        <v>0.08951476131099534</v>
       </c>
       <c r="X20" t="n">
         <v>60</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.1715244268375169</v>
+        <v>0.1678470743459353</v>
       </c>
       <c r="Z20" t="n">
         <v>58</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.07896364579607439</v>
+        <v>0.08340237280356452</v>
       </c>
       <c r="AB20" t="n">
         <v>60</v>
@@ -2239,19 +2239,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1921629736522329</v>
+        <v>0.1831799714307251</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2234193187545151</v>
+        <v>0.2218051010353467</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4331581491486892</v>
+        <v>0.4245598493034908</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2048802365307477</v>
+        <v>0.2080799365061689</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1720505692191938</v>
+        <v>0.1935416259249054</v>
       </c>
       <c r="G21" t="n">
         <v>0.2627415053689793</v>
@@ -2260,16 +2260,16 @@
         <v>0.1487949700384261</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4294769845167263</v>
+        <v>0.3758176210737486</v>
       </c>
       <c r="J21" t="n">
         <v>0.5224750540566209</v>
       </c>
       <c r="K21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L21" t="n">
-        <v>0.8064516129032258</v>
+        <v>0.8225806451612904</v>
       </c>
       <c r="M21" t="n">
         <v>16</v>
@@ -2284,37 +2284,37 @@
         <v>0.8387096774193549</v>
       </c>
       <c r="Q21" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7741935483870968</v>
+        <v>0.8064516129032258</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7741935483870968</v>
+        <v>0.8064516129032258</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1837913236988149</v>
+        <v>0.1844420786764618</v>
       </c>
       <c r="V21" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="W21" t="n">
-        <v>0.09586792949966967</v>
+        <v>0.09650445192459815</v>
       </c>
       <c r="X21" t="n">
         <v>59</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.2269495243928211</v>
+        <v>0.220460219250328</v>
       </c>
       <c r="Z21" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.1323790266670651</v>
+        <v>0.1358250341817905</v>
       </c>
       <c r="AB21" t="n">
         <v>50</v>
@@ -2327,28 +2327,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02986367253099145</v>
+        <v>0.02763702290638349</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1150149634541094</v>
+        <v>0.1150017940525584</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4051855714079088</v>
+        <v>0.3923971489063799</v>
       </c>
       <c r="E22" t="n">
-        <v>0.09837300518847283</v>
+        <v>0.0615608283154269</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0310400855877084</v>
+        <v>0.03934239639070009</v>
       </c>
       <c r="G22" t="n">
         <v>0.1070894026124833</v>
       </c>
       <c r="H22" t="n">
-        <v>0.05510638671488803</v>
+        <v>0.05510638671488804</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4041034246863612</v>
+        <v>0.3495105494398055</v>
       </c>
       <c r="J22" t="n">
         <v>0.4304461183499371</v>
@@ -2366,46 +2366,46 @@
         <v>0.4032258064516129</v>
       </c>
       <c r="O22" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5483870967741935</v>
+        <v>0.6290322580645161</v>
       </c>
       <c r="Q22" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3709677419354839</v>
+        <v>0.4354838709677419</v>
       </c>
       <c r="S22" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3870967741935484</v>
+        <v>0.4032258064516129</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1841962711555078</v>
+        <v>0.1845847231173738</v>
       </c>
       <c r="V22" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1528089838212483</v>
+        <v>0.1548505506392052</v>
       </c>
       <c r="X22" t="n">
         <v>50</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.2458362348969915</v>
+        <v>0.2280050893209173</v>
       </c>
       <c r="Z22" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.1572095365305465</v>
+        <v>0.1564724378438356</v>
       </c>
       <c r="AB22" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23">
@@ -2415,28 +2415,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1434151841436686</v>
+        <v>0.1354963238602296</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1694923646417756</v>
+        <v>0.1688612221247147</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4328870788789941</v>
+        <v>0.4179545409309852</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1932078774084578</v>
+        <v>0.1555670098567006</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1288681937542628</v>
+        <v>0.1347376252736441</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1530894940486611</v>
+        <v>0.153089494048661</v>
       </c>
       <c r="H23" t="n">
         <v>0.1394130008530467</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4040936166868785</v>
+        <v>0.3478723511626063</v>
       </c>
       <c r="J23" t="n">
         <v>0.5567383888033122</v>
@@ -2472,28 +2472,28 @@
         <v>0.7258064516129032</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2506868199584197</v>
+        <v>0.2469687660146793</v>
       </c>
       <c r="V23" t="n">
         <v>33</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1645046561855016</v>
+        <v>0.166682210357137</v>
       </c>
       <c r="X23" t="n">
         <v>48</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.3006519964685625</v>
+        <v>0.2734670415957345</v>
       </c>
       <c r="Z23" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.206396794202897</v>
+        <v>0.2009114098878049</v>
       </c>
       <c r="AB23" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24">
@@ -2503,28 +2503,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.02218714520421395</v>
+        <v>0.02070725331064444</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1095075089211576</v>
+        <v>0.1094463177711288</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3976216736097116</v>
+        <v>0.3816168687642322</v>
       </c>
       <c r="E24" t="n">
-        <v>0.09361235812726318</v>
+        <v>0.04970769952635369</v>
       </c>
       <c r="F24" t="n">
-        <v>0.02432213445552177</v>
+        <v>0.03016173283816665</v>
       </c>
       <c r="G24" t="n">
-        <v>0.09519506657712284</v>
+        <v>0.09519506657712286</v>
       </c>
       <c r="H24" t="n">
-        <v>0.05795809025261756</v>
+        <v>0.05795809025261758</v>
       </c>
       <c r="I24" t="n">
-        <v>0.391894910600414</v>
+        <v>0.3382676893032384</v>
       </c>
       <c r="J24" t="n">
         <v>0.4343508313004479</v>
@@ -2542,10 +2542,10 @@
         <v>0.3387096774193548</v>
       </c>
       <c r="O24" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P24" t="n">
-        <v>0.2741935483870968</v>
+        <v>0.2903225806451613</v>
       </c>
       <c r="Q24" t="n">
         <v>41</v>
@@ -2560,25 +2560,25 @@
         <v>0.3064516129032258</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2194290416440928</v>
+        <v>0.2185694541420376</v>
       </c>
       <c r="V24" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="W24" t="n">
-        <v>0.2000856094758694</v>
+        <v>0.2025771922070875</v>
       </c>
       <c r="X24" t="n">
         <v>44</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.2719861365285326</v>
+        <v>0.2546643186300598</v>
       </c>
       <c r="Z24" t="n">
         <v>41</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.1939160624510635</v>
+        <v>0.1938605222180586</v>
       </c>
       <c r="AB24" t="n">
         <v>41</v>
@@ -2591,37 +2591,37 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.134910498684233</v>
+        <v>0.1149203852460298</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3274811432117133</v>
+        <v>0.3235097507490151</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4301575235067765</v>
+        <v>0.4008202472932961</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3160066989679465</v>
+        <v>0.3218354776852222</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2408961392635306</v>
+        <v>0.2558047393733076</v>
       </c>
       <c r="G25" t="n">
-        <v>0.4198819832081658</v>
+        <v>0.4198819832081659</v>
       </c>
       <c r="H25" t="n">
         <v>0.2654763888308522</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2487396195443453</v>
+        <v>0.1630981845965951</v>
       </c>
       <c r="J25" t="n">
         <v>0.300018709455746</v>
       </c>
       <c r="K25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L25" t="n">
-        <v>0.7258064516129032</v>
+        <v>0.7096774193548387</v>
       </c>
       <c r="M25" t="n">
         <v>13</v>
@@ -2630,16 +2630,16 @@
         <v>0.8064516129032258</v>
       </c>
       <c r="O25" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="P25" t="n">
-        <v>0.8064516129032258</v>
+        <v>0.7096774193548387</v>
       </c>
       <c r="Q25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R25" t="n">
-        <v>0.8548387096774194</v>
+        <v>0.8387096774193549</v>
       </c>
       <c r="S25" t="n">
         <v>12</v>
@@ -2648,28 +2648,28 @@
         <v>0.8225806451612904</v>
       </c>
       <c r="U25" t="n">
-        <v>0.03002413352658418</v>
+        <v>0.02334507508805591</v>
       </c>
       <c r="V25" t="n">
         <v>60</v>
       </c>
       <c r="W25" t="n">
-        <v>0.1459358134944441</v>
+        <v>0.1452732933084691</v>
       </c>
       <c r="X25" t="n">
         <v>52</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.2757374935465507</v>
+        <v>0.2580452513372229</v>
       </c>
       <c r="Z25" t="n">
         <v>40</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.1171985789332565</v>
+        <v>0.1075825000086291</v>
       </c>
       <c r="AB25" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26">
@@ -2679,43 +2679,43 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.01005428229243791</v>
+        <v>0.009179398987246694</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0938989961932758</v>
+        <v>0.09393277906843538</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4010657113762706</v>
+        <v>0.3837628284094672</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0801688018247856</v>
+        <v>0.02011577663328862</v>
       </c>
       <c r="F26" t="n">
-        <v>0.00846643174768748</v>
+        <v>0.008534002990312971</v>
       </c>
       <c r="G26" t="n">
-        <v>0.02866595498280557</v>
+        <v>0.02866595498280556</v>
       </c>
       <c r="H26" t="n">
-        <v>0.05164853722903488</v>
+        <v>0.0516485372290349</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3930494911454814</v>
+        <v>0.3395887014542781</v>
       </c>
       <c r="J26" t="n">
         <v>0.4786186251265056</v>
       </c>
       <c r="K26" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1129032258064516</v>
+        <v>0.09677419354838709</v>
       </c>
       <c r="M26" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N26" t="n">
-        <v>0.04838709677419355</v>
+        <v>0.03225806451612903</v>
       </c>
       <c r="O26" t="n">
         <v>40</v>
@@ -2724,10 +2724,10 @@
         <v>0.3709677419354839</v>
       </c>
       <c r="Q26" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="R26" t="n">
-        <v>0.1290322580645161</v>
+        <v>0.1129032258064516</v>
       </c>
       <c r="S26" t="n">
         <v>59</v>
@@ -2736,25 +2736,25 @@
         <v>0.06451612903225806</v>
       </c>
       <c r="U26" t="n">
-        <v>0.4008295848939624</v>
+        <v>0.3912826609771002</v>
       </c>
       <c r="V26" t="n">
         <v>15</v>
       </c>
       <c r="W26" t="n">
-        <v>0.4251042594579308</v>
+        <v>0.4304610205037775</v>
       </c>
       <c r="X26" t="n">
         <v>14</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.3964555798305114</v>
+        <v>0.397696224589795</v>
       </c>
       <c r="Z26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.3731619301109829</v>
+        <v>0.3825108069075855</v>
       </c>
       <c r="AB26" t="n">
         <v>14</v>
@@ -2767,37 +2767,37 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.01325832785021473</v>
+        <v>0.01314555874387556</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1158104259409288</v>
+        <v>0.1157720960945732</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4030345921148446</v>
+        <v>0.3872773705573732</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1067852064269342</v>
+        <v>0.06820302733347985</v>
       </c>
       <c r="F27" t="n">
-        <v>0.02926098735777419</v>
+        <v>0.03710078214069178</v>
       </c>
       <c r="G27" t="n">
         <v>0.114076639781028</v>
       </c>
       <c r="H27" t="n">
-        <v>0.06536592730052965</v>
+        <v>0.06536592730052967</v>
       </c>
       <c r="I27" t="n">
-        <v>0.383303923391792</v>
+        <v>0.3319783591165993</v>
       </c>
       <c r="J27" t="n">
         <v>0.3964762099504138</v>
       </c>
       <c r="K27" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1935483870967742</v>
+        <v>0.2258064516129032</v>
       </c>
       <c r="M27" t="n">
         <v>36</v>
@@ -2806,16 +2806,16 @@
         <v>0.4354838709677419</v>
       </c>
       <c r="O27" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P27" t="n">
-        <v>0.4354838709677419</v>
+        <v>0.4838709677419355</v>
       </c>
       <c r="Q27" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="R27" t="n">
-        <v>0.4516129032258064</v>
+        <v>0.4838709677419355</v>
       </c>
       <c r="S27" t="n">
         <v>40</v>
@@ -2824,28 +2824,28 @@
         <v>0.3709677419354839</v>
       </c>
       <c r="U27" t="n">
-        <v>0.2220682041745093</v>
+        <v>0.2221592524772774</v>
       </c>
       <c r="V27" t="n">
         <v>39</v>
       </c>
       <c r="W27" t="n">
-        <v>0.2261874944299692</v>
+        <v>0.2291786890126891</v>
       </c>
       <c r="X27" t="n">
         <v>39</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.2942444895845859</v>
+        <v>0.2850708270688582</v>
       </c>
       <c r="Z27" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.2154482818057085</v>
+      </c>
+      <c r="AB27" t="n">
         <v>34</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0.2120158655061994</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="28">
@@ -2855,19 +2855,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2026186597265137</v>
+        <v>0.163385710800698</v>
       </c>
       <c r="C28" t="n">
-        <v>0.4456804047530013</v>
+        <v>0.4417964260456048</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4007207437782978</v>
+        <v>0.3621099550533907</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2449778706472534</v>
+        <v>0.3406844668589061</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2842131707160333</v>
+        <v>0.3306789924179433</v>
       </c>
       <c r="G28" t="n">
         <v>0.928208970809724</v>
@@ -2876,16 +2876,16 @@
         <v>0.08399625594578963</v>
       </c>
       <c r="I28" t="n">
-        <v>0.374909707982323</v>
+        <v>0.2508337068923183</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L28" t="n">
-        <v>0.8387096774193549</v>
+        <v>0.7903225806451613</v>
       </c>
       <c r="M28" t="n">
         <v>8</v>
@@ -2894,46 +2894,46 @@
         <v>0.8870967741935484</v>
       </c>
       <c r="O28" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="P28" t="n">
-        <v>0.3548387096774194</v>
+        <v>0.09677419354838709</v>
       </c>
       <c r="Q28" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="R28" t="n">
-        <v>0.8225806451612904</v>
+        <v>0.8709677419354839</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T28" t="n">
-        <v>0.8548387096774194</v>
+        <v>0.8709677419354839</v>
       </c>
       <c r="U28" t="n">
-        <v>0.02431435161912338</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="W28" t="n">
-        <v>0.2317362609495839</v>
+        <v>0.2345125061425517</v>
       </c>
       <c r="X28" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.1464587227040555</v>
+        <v>0.2059255299268536</v>
       </c>
       <c r="Z28" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.08402916038485037</v>
+        <v>0.1049256587343057</v>
       </c>
       <c r="AB28" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29">
@@ -2943,19 +2943,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.2891242974917798</v>
+        <v>0.2756298969779413</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3315350418183087</v>
+        <v>0.3293989583731105</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4672578453996401</v>
+        <v>0.4472009195490839</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3458345559472075</v>
+        <v>0.3337600691124034</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3051702819316164</v>
+        <v>0.3185011553351624</v>
       </c>
       <c r="G29" t="n">
         <v>0.3702950127969951</v>
@@ -2964,7 +2964,7 @@
         <v>0.298246224693777</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3728863442345142</v>
+        <v>0.3186618680382246</v>
       </c>
       <c r="J29" t="n">
         <v>0.5411617179831604</v>
@@ -2988,40 +2988,40 @@
         <v>0.8709677419354839</v>
       </c>
       <c r="Q29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R29" t="n">
-        <v>0.8709677419354839</v>
+        <v>0.8548387096774194</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T29" t="n">
-        <v>0.8709677419354839</v>
+        <v>0.8548387096774194</v>
       </c>
       <c r="U29" t="n">
-        <v>0.3534367245500948</v>
+        <v>0.3455016300708108</v>
       </c>
       <c r="V29" t="n">
         <v>22</v>
       </c>
       <c r="W29" t="n">
-        <v>0.3491812515839846</v>
+        <v>0.3543035341764009</v>
       </c>
       <c r="X29" t="n">
         <v>21</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.4148257865295828</v>
+        <v>0.4073083893876299</v>
       </c>
       <c r="Z29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.3434657180252323</v>
+        <v>0.3469832691294576</v>
       </c>
       <c r="AB29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30">
@@ -3031,28 +3031,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7196151689447498</v>
+        <v>0.6971193486764868</v>
       </c>
       <c r="C30" t="n">
-        <v>0.710118225755943</v>
+        <v>0.7042322389709574</v>
       </c>
       <c r="D30" t="n">
-        <v>0.5233579820411329</v>
+        <v>0.5143668215299512</v>
       </c>
       <c r="E30" t="n">
-        <v>0.5903579494751995</v>
+        <v>0.6548146174045421</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7020711171276699</v>
+        <v>0.7451957067021703</v>
       </c>
       <c r="G30" t="n">
         <v>0.8854391916976868</v>
       </c>
       <c r="H30" t="n">
-        <v>0.6456931749879558</v>
+        <v>0.645693174987956</v>
       </c>
       <c r="I30" t="n">
-        <v>0.4529104161588298</v>
+        <v>0.4222461254252959</v>
       </c>
       <c r="J30" t="n">
         <v>0.5713146727529083</v>
@@ -3088,25 +3088,25 @@
         <v>0.9516129032258065</v>
       </c>
       <c r="U30" t="n">
-        <v>0.6807152591960837</v>
+        <v>0.6673676674308086</v>
       </c>
       <c r="V30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W30" t="n">
-        <v>0.7650920890195674</v>
+        <v>0.7765041096680819</v>
       </c>
       <c r="X30" t="n">
         <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.5589669374557038</v>
+        <v>0.6099818728634007</v>
       </c>
       <c r="Z30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.6348135877210337</v>
+        <v>0.6719768058851631</v>
       </c>
       <c r="AB30" t="n">
         <v>5</v>
@@ -3119,31 +3119,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.715492706181349</v>
+        <v>0.6951243584122271</v>
       </c>
       <c r="C31" t="n">
-        <v>0.7153695073767228</v>
+        <v>0.7094067558916503</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5167981922162035</v>
+        <v>0.5064446924115322</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5868044490172304</v>
+        <v>0.6354915397370312</v>
       </c>
       <c r="F31" t="n">
-        <v>0.7014925597995176</v>
+        <v>0.7396042073364654</v>
       </c>
       <c r="G31" t="n">
         <v>0.8252152470298494</v>
       </c>
       <c r="H31" t="n">
-        <v>0.674811783829972</v>
+        <v>0.6748117838299721</v>
       </c>
       <c r="I31" t="n">
-        <v>0.4364180968341134</v>
+        <v>0.4103534068821569</v>
       </c>
       <c r="J31" t="n">
-        <v>0.6095969143465007</v>
+        <v>0.6095969143465005</v>
       </c>
       <c r="K31" t="n">
         <v>5</v>
@@ -3158,10 +3158,10 @@
         <v>0.9516129032258065</v>
       </c>
       <c r="O31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P31" t="n">
-        <v>0.9032258064516129</v>
+        <v>0.8870967741935484</v>
       </c>
       <c r="Q31" t="n">
         <v>5</v>
@@ -3176,25 +3176,25 @@
         <v>0.9354838709677419</v>
       </c>
       <c r="U31" t="n">
-        <v>0.6999165700575044</v>
+        <v>0.6877786171594643</v>
       </c>
       <c r="V31" t="n">
         <v>4</v>
       </c>
       <c r="W31" t="n">
-        <v>0.803964363676331</v>
+        <v>0.8158635430815903</v>
       </c>
       <c r="X31" t="n">
         <v>4</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.5721947088264434</v>
+        <v>0.6110545434675476</v>
       </c>
       <c r="Z31" t="n">
         <v>4</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.6581707138342092</v>
+        <v>0.6916081938496924</v>
       </c>
       <c r="AB31" t="n">
         <v>4</v>
@@ -3207,28 +3207,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7293522785647918</v>
+        <v>0.6996025165213099</v>
       </c>
       <c r="C32" t="n">
-        <v>0.775136966407456</v>
+        <v>0.761613263452354</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5796556551991429</v>
+        <v>0.563168705924774</v>
       </c>
       <c r="E32" t="n">
-        <v>0.7968884300532765</v>
+        <v>0.8787496229016887</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8146301082612033</v>
+        <v>0.8535335339249935</v>
       </c>
       <c r="G32" t="n">
-        <v>0.9213387244852901</v>
+        <v>0.9213387244852902</v>
       </c>
       <c r="H32" t="n">
         <v>0.7540946530344521</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3645345155688163</v>
+        <v>0.3177373314978831</v>
       </c>
       <c r="J32" t="n">
         <v>0.5373922361934172</v>
@@ -3252,10 +3252,10 @@
         <v>0.967741935483871</v>
       </c>
       <c r="Q32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R32" t="n">
-        <v>0.967741935483871</v>
+        <v>0.9838709677419355</v>
       </c>
       <c r="S32" t="n">
         <v>3</v>
@@ -3264,25 +3264,25 @@
         <v>0.967741935483871</v>
       </c>
       <c r="U32" t="n">
-        <v>0.687641460034852</v>
+        <v>0.6664622042958805</v>
       </c>
       <c r="V32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W32" t="n">
-        <v>0.8641443812205183</v>
+        <v>0.8655470417667186</v>
       </c>
       <c r="X32" t="n">
         <v>3</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.7663850233195585</v>
+        <v>0.839787259364468</v>
       </c>
       <c r="Z32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.7558661627706696</v>
+        <v>0.791338535895839</v>
       </c>
       <c r="AB32" t="n">
         <v>3</v>
@@ -3295,82 +3295,82 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.03355673734211011</v>
+        <v>0.04110728333684788</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1110811934777614</v>
+        <v>0.1148961304074945</v>
       </c>
       <c r="D33" t="n">
-        <v>0.418109184221521</v>
+        <v>0.4144735923726189</v>
       </c>
       <c r="E33" t="n">
-        <v>0.08829698028844425</v>
+        <v>0.04066400701328669</v>
       </c>
       <c r="F33" t="n">
-        <v>0.02660129163605787</v>
+        <v>0.03625345817309792</v>
       </c>
       <c r="G33" t="n">
-        <v>0.03988066053751323</v>
+        <v>0.03988066053751324</v>
       </c>
       <c r="H33" t="n">
-        <v>0.07368440263542828</v>
+        <v>0.07368440263542829</v>
       </c>
       <c r="I33" t="n">
-        <v>0.444832263005584</v>
+        <v>0.413735644260426</v>
       </c>
       <c r="J33" t="n">
         <v>0.4466931212250173</v>
       </c>
       <c r="K33" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L33" t="n">
-        <v>0.4032258064516129</v>
+        <v>0.4193548387096774</v>
       </c>
       <c r="M33" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N33" t="n">
-        <v>0.3709677419354839</v>
+        <v>0.3870967741935484</v>
       </c>
       <c r="O33" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="P33" t="n">
-        <v>0.7419354838709677</v>
+        <v>0.7903225806451613</v>
       </c>
       <c r="Q33" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="R33" t="n">
-        <v>0.2741935483870968</v>
+        <v>0.2903225806451613</v>
       </c>
       <c r="S33" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T33" t="n">
-        <v>0.3387096774193548</v>
+        <v>0.3548387096774194</v>
       </c>
       <c r="U33" t="n">
-        <v>0.2596311384999733</v>
+        <v>0.2672659967173641</v>
       </c>
       <c r="V33" t="n">
         <v>32</v>
       </c>
       <c r="W33" t="n">
-        <v>0.2381011964629558</v>
+        <v>0.2474771720541364</v>
       </c>
       <c r="X33" t="n">
         <v>35</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.286197189468804</v>
+        <v>0.269935258105963</v>
       </c>
       <c r="Z33" t="n">
         <v>38</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.2243995332408553</v>
+        <v>0.231100433518498</v>
       </c>
       <c r="AB33" t="n">
         <v>32</v>
@@ -3383,37 +3383,37 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.1195603553884284</v>
+        <v>0.1160375548816566</v>
       </c>
       <c r="C34" t="n">
-        <v>0.1451102729894833</v>
+        <v>0.1458413128006514</v>
       </c>
       <c r="D34" t="n">
-        <v>0.427968272782785</v>
+        <v>0.4145715495311579</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1554668814644841</v>
+        <v>0.1067480752657306</v>
       </c>
       <c r="F34" t="n">
-        <v>0.09582345849820317</v>
+        <v>0.1000163530514375</v>
       </c>
       <c r="G34" t="n">
         <v>0.1059193357725961</v>
       </c>
       <c r="H34" t="n">
-        <v>0.1168505452289861</v>
+        <v>0.1168505452289862</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4265441933184567</v>
+        <v>0.3782298431890248</v>
       </c>
       <c r="J34" t="n">
         <v>0.5501163381664407</v>
       </c>
       <c r="K34" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L34" t="n">
-        <v>0.7096774193548387</v>
+        <v>0.7258064516129032</v>
       </c>
       <c r="M34" t="n">
         <v>32</v>
@@ -3422,46 +3422,46 @@
         <v>0.5</v>
       </c>
       <c r="O34" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P34" t="n">
-        <v>0.7903225806451613</v>
+        <v>0.8064516129032258</v>
       </c>
       <c r="Q34" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="R34" t="n">
-        <v>0.7258064516129032</v>
+        <v>0.5967741935483871</v>
       </c>
       <c r="S34" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T34" t="n">
-        <v>0.6612903225806451</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="U34" t="n">
-        <v>0.2175647468418478</v>
+        <v>0.2191461141217687</v>
       </c>
       <c r="V34" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W34" t="n">
-        <v>0.1167834896933555</v>
+        <v>0.1201133039428817</v>
       </c>
       <c r="X34" t="n">
         <v>54</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.2574237222250983</v>
+        <v>0.2165470165722407</v>
       </c>
       <c r="Z34" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.1628438718462809</v>
+        <v>0.1538593537428591</v>
       </c>
       <c r="AB34" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35">
@@ -3471,28 +3471,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.1526662585294829</v>
+        <v>0.1522897593247697</v>
       </c>
       <c r="C35" t="n">
-        <v>0.2514642658995387</v>
+        <v>0.2511502964691218</v>
       </c>
       <c r="D35" t="n">
-        <v>0.4169767065582703</v>
+        <v>0.4046782870868488</v>
       </c>
       <c r="E35" t="n">
-        <v>0.2082838314668398</v>
+        <v>0.1979469968601238</v>
       </c>
       <c r="F35" t="n">
-        <v>0.1721231874758151</v>
+        <v>0.1917621571569491</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2957823151877945</v>
+        <v>0.2957823151877944</v>
       </c>
       <c r="H35" t="n">
         <v>0.2059151755520117</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3890295449014136</v>
+        <v>0.3516006698397937</v>
       </c>
       <c r="J35" t="n">
         <v>0.3835118582396892</v>
@@ -3510,10 +3510,10 @@
         <v>0.7741935483870968</v>
       </c>
       <c r="O35" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P35" t="n">
-        <v>0.7096774193548387</v>
+        <v>0.7258064516129032</v>
       </c>
       <c r="Q35" t="n">
         <v>14</v>
@@ -3528,28 +3528,28 @@
         <v>0.7903225806451613</v>
       </c>
       <c r="U35" t="n">
-        <v>0.2108879095649088</v>
+        <v>0.2178040069082643</v>
       </c>
       <c r="V35" t="n">
         <v>42</v>
       </c>
       <c r="W35" t="n">
-        <v>0.2313839129302518</v>
+        <v>0.2364646993330674</v>
       </c>
       <c r="X35" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.2805266485734487</v>
+        <v>0.272973461302967</v>
       </c>
       <c r="Z35" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.2038658755759715</v>
+        <v>0.2111774120253047</v>
       </c>
       <c r="AB35" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36">
@@ -3559,37 +3559,37 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.01635622719245745</v>
+        <v>0.01540004257939981</v>
       </c>
       <c r="C36" t="n">
-        <v>0.09730125418356539</v>
+        <v>0.09727642462475286</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3977646083493986</v>
+        <v>0.3804276175166734</v>
       </c>
       <c r="E36" t="n">
-        <v>0.08442725553886186</v>
+        <v>0.02644210543056839</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0136538637727466</v>
+        <v>0.01447238287816348</v>
       </c>
       <c r="G36" t="n">
-        <v>0.04176101422446857</v>
+        <v>0.04176101422446856</v>
       </c>
       <c r="H36" t="n">
-        <v>0.05637845320069207</v>
+        <v>0.05637845320069208</v>
       </c>
       <c r="I36" t="n">
-        <v>0.3890856612870125</v>
+        <v>0.3360890715055607</v>
       </c>
       <c r="J36" t="n">
         <v>0.4789978080234821</v>
       </c>
       <c r="K36" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L36" t="n">
-        <v>0.2580645161290323</v>
+        <v>0.2741935483870968</v>
       </c>
       <c r="M36" t="n">
         <v>51</v>
@@ -3598,43 +3598,43 @@
         <v>0.1935483870967742</v>
       </c>
       <c r="O36" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="P36" t="n">
-        <v>0.2903225806451613</v>
+        <v>0.2419354838709677</v>
       </c>
       <c r="Q36" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="R36" t="n">
-        <v>0.1935483870967742</v>
+        <v>0.1774193548387097</v>
       </c>
       <c r="S36" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T36" t="n">
-        <v>0.2258064516129032</v>
+        <v>0.2096774193548387</v>
       </c>
       <c r="U36" t="n">
-        <v>0.3051754999736183</v>
+        <v>0.3004656854004149</v>
       </c>
       <c r="V36" t="n">
         <v>26</v>
       </c>
       <c r="W36" t="n">
-        <v>0.2988666280480984</v>
+        <v>0.3025096928182841</v>
       </c>
       <c r="X36" t="n">
         <v>26</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.3280170337980887</v>
+        <v>0.3127066088240685</v>
       </c>
       <c r="Z36" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.2752292967426786</v>
+        <v>0.2769165905340489</v>
       </c>
       <c r="AB36" t="n">
         <v>27</v>
@@ -3647,31 +3647,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6993422090914743</v>
+        <v>0.6703802749647579</v>
       </c>
       <c r="C37" t="n">
-        <v>0.5480099946916139</v>
+        <v>0.5447699580484165</v>
       </c>
       <c r="D37" t="n">
-        <v>0.5385497983019097</v>
+        <v>0.5141371430776767</v>
       </c>
       <c r="E37" t="n">
-        <v>0.5462253170409452</v>
+        <v>0.5083663785530331</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6101791030281842</v>
+        <v>0.6129542019341092</v>
       </c>
       <c r="G37" t="n">
-        <v>0.5173950106565693</v>
+        <v>0.5173950106565695</v>
       </c>
       <c r="H37" t="n">
         <v>0.5663800905113069</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4673162462236683</v>
+        <v>0.419255637855968</v>
       </c>
       <c r="J37" t="n">
-        <v>0.9584558690611122</v>
+        <v>0.958455869061112</v>
       </c>
       <c r="K37" t="n">
         <v>6</v>
@@ -3686,10 +3686,10 @@
         <v>0.9193548387096774</v>
       </c>
       <c r="O37" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P37" t="n">
-        <v>0.9516129032258065</v>
+        <v>0.9032258064516129</v>
       </c>
       <c r="Q37" t="n">
         <v>6</v>
@@ -3704,25 +3704,25 @@
         <v>0.9193548387096774</v>
       </c>
       <c r="U37" t="n">
-        <v>0.725285409898355</v>
+        <v>0.7017334206753636</v>
       </c>
       <c r="V37" t="n">
         <v>3</v>
       </c>
       <c r="W37" t="n">
-        <v>0.5918222368050262</v>
+        <v>0.6023093159677022</v>
       </c>
       <c r="X37" t="n">
         <v>7</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.5615360712285035</v>
+        <v>0.5172059983039065</v>
       </c>
       <c r="Z37" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.6004789470241849</v>
+        <v>0.5944789437147667</v>
       </c>
       <c r="AB37" t="n">
         <v>6</v>
@@ -3735,37 +3735,37 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.008808421087818845</v>
+        <v>0.00940729705019732</v>
       </c>
       <c r="C38" t="n">
-        <v>0.09402039368416233</v>
+        <v>0.09461951939595546</v>
       </c>
       <c r="D38" t="n">
-        <v>0.4053940105303169</v>
+        <v>0.3893321459572131</v>
       </c>
       <c r="E38" t="n">
-        <v>0.08190489742838881</v>
+        <v>0.02093765078299129</v>
       </c>
       <c r="F38" t="n">
-        <v>0.008798596069716334</v>
+        <v>0.009213216501091234</v>
       </c>
       <c r="G38" t="n">
         <v>0.02092657746608599</v>
       </c>
       <c r="H38" t="n">
-        <v>0.05287357760040409</v>
+        <v>0.0528735776004041</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3985748493214707</v>
+        <v>0.3484680089737989</v>
       </c>
       <c r="J38" t="n">
         <v>0.4767923664523357</v>
       </c>
       <c r="K38" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L38" t="n">
-        <v>0.09677419354838709</v>
+        <v>0.1129032258064516</v>
       </c>
       <c r="M38" t="n">
         <v>59</v>
@@ -3780,10 +3780,10 @@
         <v>0.5806451612903226</v>
       </c>
       <c r="Q38" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="R38" t="n">
-        <v>0.1774193548387097</v>
+        <v>0.1290322580645161</v>
       </c>
       <c r="S38" t="n">
         <v>58</v>
@@ -3792,25 +3792,25 @@
         <v>0.08064516129032258</v>
       </c>
       <c r="U38" t="n">
-        <v>0.4354184408183513</v>
+        <v>0.4257551734075429</v>
       </c>
       <c r="V38" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W38" t="n">
-        <v>0.4714510628095996</v>
+        <v>0.4783528588043716</v>
       </c>
       <c r="X38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.4237281224000538</v>
+        <v>0.4306501933561255</v>
       </c>
       <c r="Z38" t="n">
         <v>11</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.4098735514361212</v>
+        <v>0.4226695037265896</v>
       </c>
       <c r="AB38" t="n">
         <v>11</v>
@@ -3823,28 +3823,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.01118078121976139</v>
+        <v>0.01179207338000899</v>
       </c>
       <c r="C39" t="n">
-        <v>0.09655667016071712</v>
+        <v>0.09702772410738726</v>
       </c>
       <c r="D39" t="n">
-        <v>0.4044041966239544</v>
+        <v>0.3878885653221904</v>
       </c>
       <c r="E39" t="n">
-        <v>0.08879895938073039</v>
+        <v>0.02959683787158477</v>
       </c>
       <c r="F39" t="n">
-        <v>0.01338176641774772</v>
+        <v>0.01427822603408573</v>
       </c>
       <c r="G39" t="n">
         <v>0.03217817112111276</v>
       </c>
       <c r="H39" t="n">
-        <v>0.05794937517519075</v>
+        <v>0.05794937517519076</v>
       </c>
       <c r="I39" t="n">
-        <v>0.393793905300387</v>
+        <v>0.343963509039895</v>
       </c>
       <c r="J39" t="n">
         <v>0.4706066749382973</v>
@@ -3862,46 +3862,46 @@
         <v>0.1612903225806452</v>
       </c>
       <c r="O39" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P39" t="n">
-        <v>0.532258064516129</v>
+        <v>0.5161290322580645</v>
       </c>
       <c r="Q39" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="R39" t="n">
-        <v>0.2903225806451613</v>
+        <v>0.2419354838709677</v>
       </c>
       <c r="S39" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T39" t="n">
-        <v>0.1774193548387097</v>
+        <v>0.1935483870967742</v>
       </c>
       <c r="U39" t="n">
-        <v>0.3645501609885945</v>
+        <v>0.3584420048627939</v>
       </c>
       <c r="V39" t="n">
         <v>19</v>
       </c>
       <c r="W39" t="n">
-        <v>0.3811997661166255</v>
+        <v>0.3867371187498831</v>
       </c>
       <c r="X39" t="n">
         <v>16</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.3786239499346251</v>
+        <v>0.374080490404737</v>
       </c>
       <c r="Z39" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.3406980452903323</v>
+        <v>0.3479695500500021</v>
       </c>
       <c r="AB39" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40">
@@ -3911,55 +3911,55 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.05403752262191767</v>
+        <v>0.05130994594934542</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1149638220262721</v>
+        <v>0.1147451468650892</v>
       </c>
       <c r="D40" t="n">
-        <v>0.4147029660381979</v>
+        <v>0.3961806919656765</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1286057567314445</v>
+        <v>0.07188627284676283</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0510033302528509</v>
+        <v>0.05125611504829453</v>
       </c>
       <c r="G40" t="n">
-        <v>0.07072382089581933</v>
+        <v>0.07072382089581936</v>
       </c>
       <c r="H40" t="n">
         <v>0.08259219276763169</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3910837869610322</v>
+        <v>0.3378246458606474</v>
       </c>
       <c r="J40" t="n">
         <v>0.5069705032149286</v>
       </c>
       <c r="K40" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L40" t="n">
-        <v>0.4677419354838709</v>
+        <v>0.5161290322580645</v>
       </c>
       <c r="M40" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N40" t="n">
-        <v>0.3870967741935484</v>
+        <v>0.3709677419354839</v>
       </c>
       <c r="O40" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P40" t="n">
-        <v>0.6774193548387096</v>
+        <v>0.6612903225806451</v>
       </c>
       <c r="Q40" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="R40" t="n">
-        <v>0.5645161290322581</v>
+        <v>0.5</v>
       </c>
       <c r="S40" t="n">
         <v>35</v>
@@ -3968,28 +3968,28 @@
         <v>0.4516129032258064</v>
       </c>
       <c r="U40" t="n">
-        <v>0.2901793879337969</v>
+        <v>0.286029281447945</v>
       </c>
       <c r="V40" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="W40" t="n">
-        <v>0.2545223997867116</v>
+        <v>0.2575797390289686</v>
       </c>
       <c r="X40" t="n">
         <v>32</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.3328518141872582</v>
+        <v>0.3095541295350807</v>
       </c>
       <c r="Z40" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.2595214032905653</v>
+        <v>0.2569240646333819</v>
       </c>
       <c r="AB40" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41">
@@ -3999,37 +3999,37 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.05783139405686143</v>
+        <v>0.05736495020440473</v>
       </c>
       <c r="C41" t="n">
-        <v>0.1769813463918891</v>
+        <v>0.1766089906566325</v>
       </c>
       <c r="D41" t="n">
-        <v>0.4013104702363791</v>
+        <v>0.3826548004546851</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1370735556052004</v>
+        <v>0.1102581482443965</v>
       </c>
       <c r="F41" t="n">
-        <v>0.08150513436701737</v>
+        <v>0.09425149944928812</v>
       </c>
       <c r="G41" t="n">
         <v>0.235728327771512</v>
       </c>
       <c r="H41" t="n">
-        <v>0.1000377324664065</v>
+        <v>0.1000377324664066</v>
       </c>
       <c r="I41" t="n">
-        <v>0.3862399855513678</v>
+        <v>0.3387209248563655</v>
       </c>
       <c r="J41" t="n">
         <v>0.3379371629923227</v>
       </c>
       <c r="K41" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L41" t="n">
-        <v>0.5645161290322581</v>
+        <v>0.5483870967741935</v>
       </c>
       <c r="M41" t="n">
         <v>23</v>
@@ -4038,43 +4038,43 @@
         <v>0.6451612903225806</v>
       </c>
       <c r="O41" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="P41" t="n">
-        <v>0.3870967741935484</v>
+        <v>0.3225806451612903</v>
       </c>
       <c r="Q41" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="R41" t="n">
-        <v>0.6612903225806451</v>
+        <v>0.6290322580645161</v>
       </c>
       <c r="S41" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T41" t="n">
-        <v>0.5806451612903226</v>
+        <v>0.5645161290322581</v>
       </c>
       <c r="U41" t="n">
-        <v>0.1729904246625682</v>
+        <v>0.177170348027705</v>
       </c>
       <c r="V41" t="n">
         <v>50</v>
       </c>
       <c r="W41" t="n">
-        <v>0.1979071195739353</v>
+        <v>0.2010895325258091</v>
       </c>
       <c r="X41" t="n">
         <v>45</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.255384458870943</v>
+        <v>0.2411856351790282</v>
       </c>
       <c r="Z41" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.1707130910685935</v>
+        <v>0.1730319575690021</v>
       </c>
       <c r="AB41" t="n">
         <v>44</v>
@@ -4087,28 +4087,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.2377721176473618</v>
+        <v>0.2252579734414215</v>
       </c>
       <c r="C42" t="n">
-        <v>0.3350516869693026</v>
+        <v>0.3324923959482997</v>
       </c>
       <c r="D42" t="n">
-        <v>0.4095099032674027</v>
+        <v>0.3846542940643613</v>
       </c>
       <c r="E42" t="n">
-        <v>0.2719886442949564</v>
+        <v>0.2623023300531036</v>
       </c>
       <c r="F42" t="n">
-        <v>0.260354024089581</v>
+        <v>0.2759785156321272</v>
       </c>
       <c r="G42" t="n">
         <v>0.3964802600300886</v>
       </c>
       <c r="H42" t="n">
-        <v>0.290361760850711</v>
+        <v>0.2903617608507111</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3360900007309864</v>
+        <v>0.278834069739235</v>
       </c>
       <c r="J42" t="n">
         <v>0.4436181966649688</v>
@@ -4126,16 +4126,16 @@
         <v>0.8387096774193549</v>
       </c>
       <c r="O42" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="P42" t="n">
-        <v>0.6451612903225806</v>
+        <v>0.3870967741935484</v>
       </c>
       <c r="Q42" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R42" t="n">
-        <v>0.8387096774193549</v>
+        <v>0.8225806451612904</v>
       </c>
       <c r="S42" t="n">
         <v>11</v>
@@ -4144,25 +4144,25 @@
         <v>0.8387096774193549</v>
       </c>
       <c r="U42" t="n">
-        <v>0.2919390133642236</v>
+        <v>0.2856338358151407</v>
       </c>
       <c r="V42" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="W42" t="n">
-        <v>0.3485679625124619</v>
+        <v>0.3530528674681963</v>
       </c>
       <c r="X42" t="n">
         <v>22</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.3362494948634881</v>
+        <v>0.3285547834597212</v>
       </c>
       <c r="Z42" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.2888232433728547</v>
+        <v>0.2931736741957908</v>
       </c>
       <c r="AB42" t="n">
         <v>24</v>
@@ -4175,19 +4175,19 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.09199345093305825</v>
+        <v>0.09359639319741167</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1593615796571494</v>
+        <v>0.1601446059533443</v>
       </c>
       <c r="D43" t="n">
-        <v>0.4255426627756518</v>
+        <v>0.4109907270814894</v>
       </c>
       <c r="E43" t="n">
-        <v>0.166657932121023</v>
+        <v>0.1207534211418434</v>
       </c>
       <c r="F43" t="n">
-        <v>0.09716218214402435</v>
+        <v>0.1035823478660907</v>
       </c>
       <c r="G43" t="n">
         <v>0.134759389259483</v>
@@ -4196,16 +4196,16 @@
         <v>0.1397182511941127</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3991197265169932</v>
+        <v>0.3600505034117562</v>
       </c>
       <c r="J43" t="n">
         <v>0.4635408841975608</v>
       </c>
       <c r="K43" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L43" t="n">
-        <v>0.6612903225806451</v>
+        <v>0.6774193548387096</v>
       </c>
       <c r="M43" t="n">
         <v>31</v>
@@ -4220,40 +4220,40 @@
         <v>0.7741935483870968</v>
       </c>
       <c r="Q43" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="R43" t="n">
-        <v>0.7419354838709677</v>
+        <v>0.6774193548387096</v>
       </c>
       <c r="S43" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T43" t="n">
-        <v>0.6774193548387096</v>
+        <v>0.6612903225806451</v>
       </c>
       <c r="U43" t="n">
-        <v>0.2779298333235067</v>
+        <v>0.2809115919090762</v>
       </c>
       <c r="V43" t="n">
         <v>30</v>
       </c>
       <c r="W43" t="n">
-        <v>0.256056030359717</v>
+        <v>0.2615838232592932</v>
       </c>
       <c r="X43" t="n">
         <v>31</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.3331868392931687</v>
+        <v>0.3121474212859008</v>
       </c>
       <c r="Z43" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.2560587214351626</v>
+        <v>0.2573308050302817</v>
       </c>
       <c r="AB43" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="44">
@@ -4263,28 +4263,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.012800627185129</v>
+        <v>0.0124226053266774</v>
       </c>
       <c r="C44" t="n">
-        <v>0.09458811827703081</v>
+        <v>0.09481329164598699</v>
       </c>
       <c r="D44" t="n">
-        <v>0.4003844698276313</v>
+        <v>0.3835600454236914</v>
       </c>
       <c r="E44" t="n">
-        <v>0.08047811700323018</v>
+        <v>0.01938290480023585</v>
       </c>
       <c r="F44" t="n">
-        <v>0.009780214330803465</v>
+        <v>0.009768839186328199</v>
       </c>
       <c r="G44" t="n">
         <v>0.02502748757149661</v>
       </c>
       <c r="H44" t="n">
-        <v>0.05325112861724622</v>
+        <v>0.05325112861724624</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3933963323370602</v>
+        <v>0.3413960842836097</v>
       </c>
       <c r="J44" t="n">
         <v>0.4865134985340695</v>
@@ -4302,43 +4302,43 @@
         <v>0.08064516129032258</v>
       </c>
       <c r="O44" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P44" t="n">
-        <v>0.3387096774193548</v>
+        <v>0.3548387096774194</v>
       </c>
       <c r="Q44" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="R44" t="n">
-        <v>0.1451612903225807</v>
+        <v>0.09677419354838709</v>
       </c>
       <c r="S44" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="T44" t="n">
-        <v>0.1129032258064516</v>
+        <v>0.09677419354838709</v>
       </c>
       <c r="U44" t="n">
-        <v>0.3586092338007782</v>
+        <v>0.3517799565730474</v>
       </c>
       <c r="V44" t="n">
         <v>20</v>
       </c>
       <c r="W44" t="n">
-        <v>0.3681355628638203</v>
+        <v>0.3730604120208577</v>
       </c>
       <c r="X44" t="n">
         <v>18</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.3646777317617673</v>
+        <v>0.3565464980259754</v>
       </c>
       <c r="Z44" t="n">
         <v>21</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.3288922177094067</v>
+        <v>0.3343648152690269</v>
       </c>
       <c r="AB44" t="n">
         <v>20</v>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.9780763661509803</v>
+        <v>0.928143635011051</v>
       </c>
       <c r="C45" t="n">
-        <v>0.829589006360112</v>
+        <v>0.8134999448935645</v>
       </c>
       <c r="D45" t="n">
-        <v>0.6318156045776399</v>
+        <v>0.5978338195977866</v>
       </c>
       <c r="E45" t="n">
         <v>1</v>
@@ -4372,7 +4372,7 @@
         <v>0.8948574719457679</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3897816627653796</v>
+        <v>0.3211814018682101</v>
       </c>
       <c r="J45" t="n">
         <v>1</v>
@@ -4408,10 +4408,10 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>1</v>
+        <v>0.9532967073477324</v>
       </c>
       <c r="V45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W45" t="n">
         <v>1</v>
@@ -4439,19 +4439,19 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.06668620445279264</v>
+        <v>0.06509102523740259</v>
       </c>
       <c r="C46" t="n">
-        <v>0.1617181773298858</v>
+        <v>0.1611587690900364</v>
       </c>
       <c r="D46" t="n">
-        <v>0.3928692968175437</v>
+        <v>0.3738916580642025</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1335002524518832</v>
+        <v>0.09823437305160775</v>
       </c>
       <c r="F46" t="n">
-        <v>0.07662401377807182</v>
+        <v>0.08581712661850129</v>
       </c>
       <c r="G46" t="n">
         <v>0.1816783426569649</v>
@@ -4460,7 +4460,7 @@
         <v>0.1167440402564721</v>
       </c>
       <c r="I46" t="n">
-        <v>0.3721048882283634</v>
+        <v>0.3228399690206425</v>
       </c>
       <c r="J46" t="n">
         <v>0.40942490449786</v>
@@ -4478,16 +4478,16 @@
         <v>0.532258064516129</v>
       </c>
       <c r="O46" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P46" t="n">
-        <v>0.1774193548387097</v>
+        <v>0.1612903225806452</v>
       </c>
       <c r="Q46" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="R46" t="n">
-        <v>0.6129032258064516</v>
+        <v>0.5806451612903226</v>
       </c>
       <c r="S46" t="n">
         <v>30</v>
@@ -4496,25 +4496,25 @@
         <v>0.532258064516129</v>
       </c>
       <c r="U46" t="n">
-        <v>0.2387074095046538</v>
+        <v>0.2388865917540891</v>
       </c>
       <c r="V46" t="n">
         <v>35</v>
       </c>
       <c r="W46" t="n">
-        <v>0.2453093033505311</v>
+        <v>0.2485378646949557</v>
       </c>
       <c r="X46" t="n">
         <v>34</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.2914311678522609</v>
+        <v>0.2786014898212415</v>
       </c>
       <c r="Z46" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.2218383430957597</v>
+        <v>0.2246874286787045</v>
       </c>
       <c r="AB46" t="n">
         <v>33</v>
@@ -4527,19 +4527,19 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.01879163299541776</v>
+        <v>0.01768656467853381</v>
       </c>
       <c r="C47" t="n">
-        <v>0.1176216372036968</v>
+        <v>0.117281537976181</v>
       </c>
       <c r="D47" t="n">
-        <v>0.3899559189211388</v>
+        <v>0.3723481362871403</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0930218341021342</v>
+        <v>0.05221717627129522</v>
       </c>
       <c r="F47" t="n">
-        <v>0.02635701255271719</v>
+        <v>0.03342544822355974</v>
       </c>
       <c r="G47" t="n">
         <v>0.1211897457909047</v>
@@ -4548,10 +4548,10 @@
         <v>0.06313236499153477</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3811488796328082</v>
+        <v>0.3280540153540136</v>
       </c>
       <c r="J47" t="n">
-        <v>0.4062551645507752</v>
+        <v>0.4062551645507753</v>
       </c>
       <c r="K47" t="n">
         <v>45</v>
@@ -4566,43 +4566,43 @@
         <v>0.4516129032258064</v>
       </c>
       <c r="O47" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P47" t="n">
-        <v>0.1290322580645161</v>
+        <v>0.1451612903225807</v>
       </c>
       <c r="Q47" t="n">
+        <v>39</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0.3870967741935484</v>
+      </c>
+      <c r="S47" t="n">
         <v>42</v>
       </c>
-      <c r="R47" t="n">
+      <c r="T47" t="n">
         <v>0.3387096774193548</v>
       </c>
-      <c r="S47" t="n">
-        <v>43</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0.3225806451612903</v>
-      </c>
       <c r="U47" t="n">
-        <v>0.202872894827944</v>
+        <v>0.2030655108169831</v>
       </c>
       <c r="V47" t="n">
         <v>43</v>
       </c>
       <c r="W47" t="n">
-        <v>0.1966168081641973</v>
+        <v>0.1987531903440971</v>
       </c>
       <c r="X47" t="n">
         <v>46</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.2622992732325173</v>
+        <v>0.2458434599297599</v>
       </c>
       <c r="Z47" t="n">
         <v>42</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.1832277175989303</v>
+        <v>0.1835523511035449</v>
       </c>
       <c r="AB47" t="n">
         <v>42</v>
@@ -4618,25 +4618,25 @@
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0912791820559133</v>
+        <v>0.09150675810169713</v>
       </c>
       <c r="D48" t="n">
-        <v>0.399779121411482</v>
+        <v>0.3831952110531123</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0699528297435663</v>
+        <v>0.00846592469334911</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0.01421041524078086</v>
+        <v>0.01421041524078085</v>
       </c>
       <c r="H48" t="n">
-        <v>0.04990409430041925</v>
+        <v>0.04990409430041927</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3938303640716613</v>
+        <v>0.3413904388415208</v>
       </c>
       <c r="J48" t="n">
         <v>0.4713183549886679</v>
@@ -4654,16 +4654,16 @@
         <v>0.01612903225806452</v>
       </c>
       <c r="O48" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P48" t="n">
-        <v>0.3225806451612903</v>
+        <v>0.3387096774193548</v>
       </c>
       <c r="Q48" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="R48" t="n">
-        <v>0.06451612903225806</v>
+        <v>0.03225806451612903</v>
       </c>
       <c r="S48" t="n">
         <v>62</v>
@@ -4672,25 +4672,25 @@
         <v>0.01612903225806452</v>
       </c>
       <c r="U48" t="n">
-        <v>0.5503618575209929</v>
+        <v>0.5340638320583172</v>
       </c>
       <c r="V48" t="n">
         <v>8</v>
       </c>
       <c r="W48" t="n">
-        <v>0.6270481049475094</v>
+        <v>0.6353615961968049</v>
       </c>
       <c r="X48" t="n">
         <v>6</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.4999806336247171</v>
+        <v>0.5289236480144101</v>
       </c>
       <c r="Z48" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.5260858003438784</v>
+        <v>0.5486812845620131</v>
       </c>
       <c r="AB48" t="n">
         <v>7</v>
@@ -4703,37 +4703,37 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.007602634284363627</v>
+        <v>0.007937565485284686</v>
       </c>
       <c r="C49" t="n">
-        <v>0.09647819503562845</v>
+        <v>0.09670337035783381</v>
       </c>
       <c r="D49" t="n">
-        <v>0.3973829261239529</v>
+        <v>0.3805021980484863</v>
       </c>
       <c r="E49" t="n">
-        <v>0.08165200130557916</v>
+        <v>0.02520584914108694</v>
       </c>
       <c r="F49" t="n">
-        <v>0.009327209423159337</v>
+        <v>0.01117964742310905</v>
       </c>
       <c r="G49" t="n">
-        <v>0.04481688330030308</v>
+        <v>0.04481688330030306</v>
       </c>
       <c r="H49" t="n">
-        <v>0.05587713272716344</v>
+        <v>0.05587713272716346</v>
       </c>
       <c r="I49" t="n">
-        <v>0.3885055467142973</v>
+        <v>0.3376491971725076</v>
       </c>
       <c r="J49" t="n">
         <v>0.4572431254560564</v>
       </c>
       <c r="K49" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L49" t="n">
-        <v>0.06451612903225806</v>
+        <v>0.08064516129032258</v>
       </c>
       <c r="M49" t="n">
         <v>54</v>
@@ -4742,10 +4742,10 @@
         <v>0.1451612903225807</v>
       </c>
       <c r="O49" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P49" t="n">
-        <v>0.2419354838709677</v>
+        <v>0.2580645161290323</v>
       </c>
       <c r="Q49" t="n">
         <v>53</v>
@@ -4754,31 +4754,31 @@
         <v>0.1612903225806452</v>
       </c>
       <c r="S49" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="T49" t="n">
-        <v>0.09677419354838709</v>
+        <v>0.1129032258064516</v>
       </c>
       <c r="U49" t="n">
-        <v>0.2704901543845801</v>
+        <v>0.268462179680248</v>
       </c>
       <c r="V49" t="n">
         <v>31</v>
       </c>
       <c r="W49" t="n">
-        <v>0.2654280918060282</v>
+        <v>0.2690207952817056</v>
       </c>
       <c r="X49" t="n">
         <v>30</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.3074409338163255</v>
+        <v>0.2890786233371062</v>
       </c>
       <c r="Z49" t="n">
         <v>31</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.2451329641229873</v>
+        <v>0.2457501345517074</v>
       </c>
       <c r="AB49" t="n">
         <v>31</v>
@@ -4791,28 +4791,28 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.01182462277322826</v>
+        <v>0.01219580399284818</v>
       </c>
       <c r="C50" t="n">
-        <v>0.09666945809728179</v>
+        <v>0.09710850404736406</v>
       </c>
       <c r="D50" t="n">
-        <v>0.4037782239647834</v>
+        <v>0.3874585018462353</v>
       </c>
       <c r="E50" t="n">
-        <v>0.08778395279995889</v>
+        <v>0.03036490234157984</v>
       </c>
       <c r="F50" t="n">
-        <v>0.01323645980286167</v>
+        <v>0.01473677951932892</v>
       </c>
       <c r="G50" t="n">
         <v>0.03879307573970747</v>
       </c>
       <c r="H50" t="n">
-        <v>0.05614395569306287</v>
+        <v>0.05614395569306288</v>
       </c>
       <c r="I50" t="n">
-        <v>0.3941488704830005</v>
+        <v>0.3438179530208731</v>
       </c>
       <c r="J50" t="n">
         <v>0.4668970953311947</v>
@@ -4830,43 +4830,43 @@
         <v>0.1774193548387097</v>
       </c>
       <c r="O50" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P50" t="n">
-        <v>0.4838709677419355</v>
+        <v>0.5</v>
       </c>
       <c r="Q50" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R50" t="n">
-        <v>0.2419354838709677</v>
+        <v>0.2580645161290323</v>
       </c>
       <c r="S50" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="T50" t="n">
-        <v>0.1612903225806452</v>
+        <v>0.2258064516129032</v>
       </c>
       <c r="U50" t="n">
-        <v>0.3862613489018079</v>
+        <v>0.3788695124995178</v>
       </c>
       <c r="V50" t="n">
         <v>17</v>
       </c>
       <c r="W50" t="n">
-        <v>0.4083315788466247</v>
+        <v>0.4141795580339642</v>
       </c>
       <c r="X50" t="n">
         <v>15</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.3924860041977052</v>
+        <v>0.3936244512981265</v>
       </c>
       <c r="Z50" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.3617597894419622</v>
+        <v>0.371491360527698</v>
       </c>
       <c r="AB50" t="n">
         <v>15</v>
@@ -4879,31 +4879,31 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.02619025496978723</v>
+        <v>0.0272408846723942</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1081387281506602</v>
+        <v>0.108757917880633</v>
       </c>
       <c r="D51" t="n">
-        <v>0.4152645937488926</v>
+        <v>0.3987305431305171</v>
       </c>
       <c r="E51" t="n">
-        <v>0.1166276810336621</v>
+        <v>0.06353133231535082</v>
       </c>
       <c r="F51" t="n">
-        <v>0.03422973584784461</v>
+        <v>0.0372351045258977</v>
       </c>
       <c r="G51" t="n">
         <v>0.07020303218747889</v>
       </c>
       <c r="H51" t="n">
-        <v>0.07119640431390575</v>
+        <v>0.07119640431390577</v>
       </c>
       <c r="I51" t="n">
-        <v>0.3949036573732944</v>
+        <v>0.3476750983899713</v>
       </c>
       <c r="J51" t="n">
-        <v>0.4521415197890517</v>
+        <v>0.4521415197890518</v>
       </c>
       <c r="K51" t="n">
         <v>40</v>
@@ -4912,10 +4912,10 @@
         <v>0.3709677419354839</v>
       </c>
       <c r="M51" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N51" t="n">
-        <v>0.3064516129032258</v>
+        <v>0.3225806451612903</v>
       </c>
       <c r="O51" t="n">
         <v>20</v>
@@ -4924,40 +4924,40 @@
         <v>0.6935483870967742</v>
       </c>
       <c r="Q51" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R51" t="n">
-        <v>0.4838709677419355</v>
+        <v>0.4677419354838709</v>
       </c>
       <c r="S51" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T51" t="n">
-        <v>0.4032258064516129</v>
+        <v>0.3870967741935484</v>
       </c>
       <c r="U51" t="n">
-        <v>0.3052956060557226</v>
+        <v>0.303244589262894</v>
       </c>
       <c r="V51" t="n">
         <v>25</v>
       </c>
       <c r="W51" t="n">
-        <v>0.3024270517234139</v>
+        <v>0.3073700160593162</v>
       </c>
       <c r="X51" t="n">
         <v>25</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.3531700005119936</v>
+        <v>0.3417582298784445</v>
       </c>
       <c r="Z51" t="n">
         <v>23</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.2872225491001896</v>
+        <v>0.2911262046632599</v>
       </c>
       <c r="AB51" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="52">
@@ -4967,37 +4967,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.006312797055932696</v>
+        <v>0.005191918856012641</v>
       </c>
       <c r="C52" t="n">
-        <v>0.11075468267672</v>
+        <v>0.1101435118643668</v>
       </c>
       <c r="D52" t="n">
-        <v>0.3643006311244554</v>
+        <v>0.3440135573593826</v>
       </c>
       <c r="E52" t="n">
-        <v>0.04754154774001326</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>0.00128177964731746</v>
+        <v>0.00672647468228329</v>
       </c>
       <c r="G52" t="n">
         <v>0.1165398610274509</v>
       </c>
       <c r="H52" t="n">
-        <v>0.04757007336992405</v>
+        <v>0.04757007336992406</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3821917427814498</v>
+        <v>0.3277597673652143</v>
       </c>
       <c r="J52" t="n">
-        <v>0.3972264019870716</v>
+        <v>0.3972264019870717</v>
       </c>
       <c r="K52" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L52" t="n">
-        <v>0.04838709677419355</v>
+        <v>0.03225806451612903</v>
       </c>
       <c r="M52" t="n">
         <v>41</v>
@@ -5012,40 +5012,40 @@
         <v>0.06451612903225806</v>
       </c>
       <c r="Q52" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R52" t="n">
-        <v>0.03225806451612903</v>
+        <v>0.01612903225806452</v>
       </c>
       <c r="S52" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="T52" t="n">
-        <v>0.03225806451612903</v>
+        <v>0.04838709677419355</v>
       </c>
       <c r="U52" t="n">
-        <v>0.2381736346885583</v>
+        <v>0.2360521602645237</v>
       </c>
       <c r="V52" t="n">
         <v>36</v>
       </c>
       <c r="W52" t="n">
-        <v>0.2486047014816639</v>
+        <v>0.25086361073666</v>
       </c>
       <c r="X52" t="n">
         <v>33</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.2508261291446566</v>
+        <v>0.235255172177686</v>
       </c>
       <c r="Z52" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.2049846223784684</v>
+        <v>0.2068393031041845</v>
       </c>
       <c r="AB52" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="53">
@@ -5055,28 +5055,28 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.06546316549364463</v>
+        <v>0.06263642942043003</v>
       </c>
       <c r="C53" t="n">
-        <v>0.1189759379007978</v>
+        <v>0.1189903753848089</v>
       </c>
       <c r="D53" t="n">
-        <v>0.4245957874048744</v>
+        <v>0.4064041038270429</v>
       </c>
       <c r="E53" t="n">
-        <v>0.142416367976695</v>
+        <v>0.0859964558290843</v>
       </c>
       <c r="F53" t="n">
-        <v>0.06193282106669581</v>
+        <v>0.06222932294703055</v>
       </c>
       <c r="G53" t="n">
         <v>0.07521126532302679</v>
       </c>
       <c r="H53" t="n">
-        <v>0.08680611110935829</v>
+        <v>0.08680611110935831</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3996141304017544</v>
+        <v>0.347310637046079</v>
       </c>
       <c r="J53" t="n">
         <v>0.5155570019503907</v>
@@ -5094,46 +5094,46 @@
         <v>0.4677419354838709</v>
       </c>
       <c r="O53" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P53" t="n">
-        <v>0.7580645161290323</v>
+        <v>0.7419354838709677</v>
       </c>
       <c r="Q53" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="R53" t="n">
-        <v>0.6774193548387096</v>
+        <v>0.5161290322580645</v>
       </c>
       <c r="S53" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="T53" t="n">
-        <v>0.5161290322580645</v>
+        <v>0.4677419354838709</v>
       </c>
       <c r="U53" t="n">
-        <v>0.2438275268357347</v>
+        <v>0.2423505753028637</v>
       </c>
       <c r="V53" t="n">
         <v>34</v>
       </c>
       <c r="W53" t="n">
-        <v>0.1852788579838525</v>
+        <v>0.1878698642936773</v>
       </c>
       <c r="X53" t="n">
         <v>47</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.3050904608969898</v>
+        <v>0.27163060098272</v>
       </c>
       <c r="Z53" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AA53" t="n">
-        <v>0.2120730211778927</v>
+        <v>0.2048746859102114</v>
       </c>
       <c r="AB53" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="54">
@@ -5143,19 +5143,19 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.05587101276168333</v>
+        <v>0.05037425841559628</v>
       </c>
       <c r="C54" t="n">
-        <v>0.1829598726663651</v>
+        <v>0.1812364824082698</v>
       </c>
       <c r="D54" t="n">
-        <v>0.3341500573018881</v>
+        <v>0.3109603049455307</v>
       </c>
       <c r="E54" t="n">
-        <v>0.07549419135871219</v>
+        <v>0.05189797535872737</v>
       </c>
       <c r="F54" t="n">
-        <v>0.05884043575289743</v>
+        <v>0.07227646889899857</v>
       </c>
       <c r="G54" t="n">
         <v>0.2425535453330726</v>
@@ -5164,16 +5164,16 @@
         <v>0.111926754765155</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3403030365211646</v>
+        <v>0.2806890052540924</v>
       </c>
       <c r="J54" t="n">
         <v>0.3607300534975069</v>
       </c>
       <c r="K54" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L54" t="n">
-        <v>0.5161290322580645</v>
+        <v>0.5</v>
       </c>
       <c r="M54" t="n">
         <v>22</v>
@@ -5188,40 +5188,40 @@
         <v>0.03225806451612903</v>
       </c>
       <c r="Q54" t="n">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="R54" t="n">
-        <v>0.09677419354838709</v>
+        <v>0.3709677419354839</v>
       </c>
       <c r="S54" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T54" t="n">
-        <v>0.4838709677419355</v>
+        <v>0.5</v>
       </c>
       <c r="U54" t="n">
-        <v>0.1894662942222624</v>
+        <v>0.1872395685478882</v>
       </c>
       <c r="V54" t="n">
         <v>46</v>
       </c>
       <c r="W54" t="n">
-        <v>0.2313840358637151</v>
+        <v>0.2329075558263879</v>
       </c>
       <c r="X54" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.2059528455075887</v>
+        <v>0.1970436168397286</v>
       </c>
       <c r="Z54" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AA54" t="n">
-        <v>0.1643972047891849</v>
+        <v>0.1683849230036981</v>
       </c>
       <c r="AB54" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="55">
@@ -5231,37 +5231,37 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.1882187298634909</v>
+        <v>0.1723817827492499</v>
       </c>
       <c r="C55" t="n">
-        <v>0.3562570150796388</v>
+        <v>0.3539292510897993</v>
       </c>
       <c r="D55" t="n">
-        <v>0.3035362420119612</v>
+        <v>0.2658974418027623</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>0.01874899727120017</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1446293921471688</v>
+        <v>0.1769665239103047</v>
       </c>
       <c r="G55" t="n">
-        <v>0.6157118308767582</v>
+        <v>0.6157118308767583</v>
       </c>
       <c r="H55" t="n">
         <v>0.1194300841660211</v>
       </c>
       <c r="I55" t="n">
-        <v>0.4156487519944667</v>
+        <v>0.3453770307292289</v>
       </c>
       <c r="J55" t="n">
         <v>0.2037851498082547</v>
       </c>
       <c r="K55" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L55" t="n">
-        <v>0.7903225806451613</v>
+        <v>0.8064516129032258</v>
       </c>
       <c r="M55" t="n">
         <v>10</v>
@@ -5276,25 +5276,25 @@
         <v>0.01612903225806452</v>
       </c>
       <c r="Q55" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="R55" t="n">
-        <v>0.01612903225806452</v>
+        <v>0.08064516129032258</v>
       </c>
       <c r="S55" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T55" t="n">
-        <v>0.7580645161290323</v>
+        <v>0.7741935483870968</v>
       </c>
       <c r="U55" t="n">
-        <v>0.1533484256509779</v>
+        <v>0.1477695730282641</v>
       </c>
       <c r="V55" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="W55" t="n">
-        <v>0.2747512774568808</v>
+        <v>0.2790197131042491</v>
       </c>
       <c r="X55" t="n">
         <v>29</v>
@@ -5306,10 +5306,10 @@
         <v>62</v>
       </c>
       <c r="AA55" t="n">
-        <v>0.07558154262272404</v>
+        <v>0.08834959935720474</v>
       </c>
       <c r="AB55" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="56">
@@ -5319,28 +5319,28 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.1513878158761139</v>
+        <v>0.1442557443239006</v>
       </c>
       <c r="C56" t="n">
-        <v>0.2571167918238885</v>
+        <v>0.2557781883274478</v>
       </c>
       <c r="D56" t="n">
-        <v>0.3855468484395942</v>
+        <v>0.3551689580991449</v>
       </c>
       <c r="E56" t="n">
-        <v>0.1256362057959477</v>
+        <v>0.09485947968049503</v>
       </c>
       <c r="F56" t="n">
-        <v>0.1411592113543883</v>
+        <v>0.1529100548524946</v>
       </c>
       <c r="G56" t="n">
-        <v>0.3802447044835605</v>
+        <v>0.3802447044835606</v>
       </c>
       <c r="H56" t="n">
         <v>0.111541384759202</v>
       </c>
       <c r="I56" t="n">
-        <v>0.4235211314512527</v>
+        <v>0.3699900921212831</v>
       </c>
       <c r="J56" t="n">
         <v>0.356042812156856</v>
@@ -5358,16 +5358,16 @@
         <v>0.7903225806451613</v>
       </c>
       <c r="O56" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P56" t="n">
-        <v>0.1129032258064516</v>
+        <v>0.08064516129032258</v>
       </c>
       <c r="Q56" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R56" t="n">
-        <v>0.532258064516129</v>
+        <v>0.5483870967741935</v>
       </c>
       <c r="S56" t="n">
         <v>17</v>
@@ -5376,25 +5376,25 @@
         <v>0.7419354838709677</v>
       </c>
       <c r="U56" t="n">
-        <v>0.1933734694896495</v>
+        <v>0.1936678759322911</v>
       </c>
       <c r="V56" t="n">
         <v>45</v>
       </c>
       <c r="W56" t="n">
-        <v>0.2197532745187698</v>
+        <v>0.2231037520210457</v>
       </c>
       <c r="X56" t="n">
         <v>40</v>
       </c>
       <c r="Y56" t="n">
-        <v>0.1850197239550371</v>
+        <v>0.1512430828525294</v>
       </c>
       <c r="Z56" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="AA56" t="n">
-        <v>0.1532307198686087</v>
+        <v>0.1492378630471011</v>
       </c>
       <c r="AB56" t="n">
         <v>49</v>
@@ -5407,19 +5407,19 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.1072869072138623</v>
+        <v>0.09891823550755639</v>
       </c>
       <c r="C57" t="n">
-        <v>0.2174112946136334</v>
+        <v>0.2161147484926656</v>
       </c>
       <c r="D57" t="n">
-        <v>0.3540025215202017</v>
+        <v>0.3249123658918641</v>
       </c>
       <c r="E57" t="n">
-        <v>0.06049753982904994</v>
+        <v>0.03648465088505763</v>
       </c>
       <c r="F57" t="n">
-        <v>0.08415478292503946</v>
+        <v>0.0984928386888643</v>
       </c>
       <c r="G57" t="n">
         <v>0.3398791053164789</v>
@@ -5428,7 +5428,7 @@
         <v>0.05950444202713696</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4268448529109167</v>
+        <v>0.3657973523192093</v>
       </c>
       <c r="J57" t="n">
         <v>0.345468045407344</v>
@@ -5452,40 +5452,40 @@
         <v>0.04838709677419355</v>
       </c>
       <c r="Q57" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="R57" t="n">
-        <v>0.04838709677419355</v>
+        <v>0.2741935483870968</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="T57" t="n">
-        <v>0.6129032258064516</v>
+        <v>0.5806451612903226</v>
       </c>
       <c r="U57" t="n">
-        <v>0.1369319970209936</v>
+        <v>0.1365222462705548</v>
       </c>
       <c r="V57" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="W57" t="n">
-        <v>0.1462652701588642</v>
+        <v>0.1479832905992687</v>
       </c>
       <c r="X57" t="n">
         <v>51</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.1132158577388624</v>
+        <v>0.08348875858978798</v>
       </c>
       <c r="Z57" t="n">
         <v>61</v>
       </c>
       <c r="AA57" t="n">
-        <v>0.08209043292600487</v>
+        <v>0.07864345517702526</v>
       </c>
       <c r="AB57" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="58">
@@ -5495,28 +5495,28 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.01459285078312333</v>
+        <v>0.01382622998201063</v>
       </c>
       <c r="C58" t="n">
-        <v>0.09500415367046776</v>
+        <v>0.09515294336806156</v>
       </c>
       <c r="D58" t="n">
-        <v>0.4039009551431969</v>
+        <v>0.3866890086269894</v>
       </c>
       <c r="E58" t="n">
-        <v>0.08551157085722437</v>
+        <v>0.02390441353493122</v>
       </c>
       <c r="F58" t="n">
-        <v>0.01254701465353101</v>
+        <v>0.01207202522267133</v>
       </c>
       <c r="G58" t="n">
         <v>0.02389981727454032</v>
       </c>
       <c r="H58" t="n">
-        <v>0.05376225960671926</v>
+        <v>0.05376225960671928</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3949788090012022</v>
+        <v>0.3422466500262616</v>
       </c>
       <c r="J58" t="n">
         <v>0.4895973986071274</v>
@@ -5534,43 +5534,43 @@
         <v>0.1129032258064516</v>
       </c>
       <c r="O58" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P58" t="n">
-        <v>0.5</v>
+        <v>0.4677419354838709</v>
       </c>
       <c r="Q58" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="R58" t="n">
-        <v>0.2096774193548387</v>
+        <v>0.1451612903225807</v>
       </c>
       <c r="S58" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="T58" t="n">
-        <v>0.1451612903225807</v>
+        <v>0.1290322580645161</v>
       </c>
       <c r="U58" t="n">
-        <v>0.4294680258827999</v>
+        <v>0.4188678913364022</v>
       </c>
       <c r="V58" t="n">
         <v>13</v>
       </c>
       <c r="W58" t="n">
-        <v>0.4571997640407851</v>
+        <v>0.4631921211469252</v>
       </c>
       <c r="X58" t="n">
         <v>13</v>
       </c>
       <c r="Y58" t="n">
-        <v>0.4186523853563711</v>
+        <v>0.4227345942574097</v>
       </c>
       <c r="Z58" t="n">
         <v>12</v>
       </c>
       <c r="AA58" t="n">
-        <v>0.4015724909236211</v>
+        <v>0.4124260418414648</v>
       </c>
       <c r="AB58" t="n">
         <v>12</v>
@@ -5583,19 +5583,19 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.1926660652087183</v>
+        <v>0.1837823278611346</v>
       </c>
       <c r="C59" t="n">
-        <v>0.1922732596372402</v>
+        <v>0.1914692772299434</v>
       </c>
       <c r="D59" t="n">
-        <v>0.4551018111846865</v>
+        <v>0.4332278844659108</v>
       </c>
       <c r="E59" t="n">
-        <v>0.2391198144741781</v>
+        <v>0.1761794539905956</v>
       </c>
       <c r="F59" t="n">
-        <v>0.172848138230889</v>
+        <v>0.1688658586757274</v>
       </c>
       <c r="G59" t="n">
         <v>0.145286884271392</v>
@@ -5604,16 +5604,16 @@
         <v>0.1866744001297166</v>
       </c>
       <c r="I59" t="n">
-        <v>0.4000284633783942</v>
+        <v>0.3466561447193072</v>
       </c>
       <c r="J59" t="n">
-        <v>0.6326355880901644</v>
+        <v>0.6326355880901643</v>
       </c>
       <c r="K59" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L59" t="n">
-        <v>0.8225806451612904</v>
+        <v>0.8387096774193549</v>
       </c>
       <c r="M59" t="n">
         <v>19</v>
@@ -5628,40 +5628,40 @@
         <v>0.8548387096774194</v>
       </c>
       <c r="Q59" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="R59" t="n">
-        <v>0.8064516129032258</v>
+        <v>0.7741935483870968</v>
       </c>
       <c r="S59" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="T59" t="n">
-        <v>0.8064516129032258</v>
+        <v>0.7580645161290323</v>
       </c>
       <c r="U59" t="n">
-        <v>0.3774242545712791</v>
+        <v>0.3688368283897112</v>
       </c>
       <c r="V59" t="n">
         <v>18</v>
       </c>
       <c r="W59" t="n">
-        <v>0.2938591359545035</v>
+        <v>0.2978898243203298</v>
       </c>
       <c r="X59" t="n">
         <v>27</v>
       </c>
       <c r="Y59" t="n">
-        <v>0.3987225859166605</v>
+        <v>0.3595666735266591</v>
       </c>
       <c r="Z59" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AA59" t="n">
-        <v>0.328382483170194</v>
+        <v>0.3191330225073997</v>
       </c>
       <c r="AB59" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="60">
@@ -5671,37 +5671,37 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.02325076028657164</v>
+        <v>0.02214483128054311</v>
       </c>
       <c r="C60" t="n">
-        <v>0.09787074620009373</v>
+        <v>0.09804097168965217</v>
       </c>
       <c r="D60" t="n">
-        <v>0.4029044836441037</v>
+        <v>0.3854880293210091</v>
       </c>
       <c r="E60" t="n">
-        <v>0.08825987855472087</v>
+        <v>0.02806524474578989</v>
       </c>
       <c r="F60" t="n">
-        <v>0.01768435512891509</v>
+        <v>0.01774173980714943</v>
       </c>
       <c r="G60" t="n">
-        <v>0.03673964802445983</v>
+        <v>0.03673964802445982</v>
       </c>
       <c r="H60" t="n">
-        <v>0.05574769723744734</v>
+        <v>0.05574769723744735</v>
       </c>
       <c r="I60" t="n">
-        <v>0.3974436054917919</v>
+        <v>0.3448111492909999</v>
       </c>
       <c r="J60" t="n">
         <v>0.4918713691661808</v>
       </c>
       <c r="K60" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L60" t="n">
-        <v>0.3387096774193548</v>
+        <v>0.3548387096774194</v>
       </c>
       <c r="M60" t="n">
         <v>50</v>
@@ -5716,40 +5716,40 @@
         <v>0.4193548387096774</v>
       </c>
       <c r="Q60" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="R60" t="n">
-        <v>0.2580645161290323</v>
+        <v>0.2096774193548387</v>
       </c>
       <c r="S60" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="T60" t="n">
-        <v>0.2580645161290323</v>
+        <v>0.2419354838709677</v>
       </c>
       <c r="U60" t="n">
-        <v>0.3567103628751925</v>
+        <v>0.3496673999461191</v>
       </c>
       <c r="V60" t="n">
         <v>21</v>
       </c>
       <c r="W60" t="n">
-        <v>0.3561548685664022</v>
+        <v>0.3608901096289199</v>
       </c>
       <c r="X60" t="n">
         <v>20</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.363073438687507</v>
+        <v>0.3536063004660277</v>
       </c>
       <c r="Z60" t="n">
         <v>22</v>
       </c>
       <c r="AA60" t="n">
-        <v>0.3240966751992451</v>
+        <v>0.3287543389322804</v>
       </c>
       <c r="AB60" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="61">
@@ -5759,37 +5759,37 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.0227632047748552</v>
+        <v>0.02144914396966553</v>
       </c>
       <c r="C61" t="n">
-        <v>0.09842125191284309</v>
+        <v>0.09844519645347835</v>
       </c>
       <c r="D61" t="n">
-        <v>0.3937973469880468</v>
+        <v>0.3757601098469705</v>
       </c>
       <c r="E61" t="n">
-        <v>0.07749428793223113</v>
+        <v>0.01798922160958182</v>
       </c>
       <c r="F61" t="n">
-        <v>0.0134679245951554</v>
+        <v>0.01395452772667584</v>
       </c>
       <c r="G61" t="n">
-        <v>0.04496212871214112</v>
+        <v>0.04496212871214113</v>
       </c>
       <c r="H61" t="n">
-        <v>0.05449374904598057</v>
+        <v>0.05449374904598058</v>
       </c>
       <c r="I61" t="n">
-        <v>0.3959588598910436</v>
+        <v>0.3427836344430502</v>
       </c>
       <c r="J61" t="n">
         <v>0.485285866746701</v>
       </c>
       <c r="K61" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L61" t="n">
-        <v>0.3225806451612903</v>
+        <v>0.3387096774193548</v>
       </c>
       <c r="M61" t="n">
         <v>48</v>
@@ -5798,46 +5798,46 @@
         <v>0.2419354838709677</v>
       </c>
       <c r="O61" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P61" t="n">
-        <v>0.1935483870967742</v>
+        <v>0.1774193548387097</v>
       </c>
       <c r="Q61" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="R61" t="n">
-        <v>0.1129032258064516</v>
+        <v>0.06451612903225806</v>
       </c>
       <c r="S61" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="T61" t="n">
-        <v>0.1935483870967742</v>
+        <v>0.1774193548387097</v>
       </c>
       <c r="U61" t="n">
-        <v>0.3255569877438948</v>
+        <v>0.3197704244775977</v>
       </c>
       <c r="V61" t="n">
         <v>24</v>
       </c>
       <c r="W61" t="n">
-        <v>0.3177447188986979</v>
+        <v>0.321739280851706</v>
       </c>
       <c r="X61" t="n">
         <v>24</v>
       </c>
       <c r="Y61" t="n">
-        <v>0.3304068903682705</v>
+        <v>0.3157876150175261</v>
       </c>
       <c r="Z61" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AA61" t="n">
-        <v>0.2884785646081588</v>
+        <v>0.2909076420355646</v>
       </c>
       <c r="AB61" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="62">
@@ -5847,37 +5847,37 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.01366700006784611</v>
+        <v>0.01279703889960636</v>
       </c>
       <c r="C62" t="n">
-        <v>0.09492475211586317</v>
+        <v>0.09498860960270333</v>
       </c>
       <c r="D62" t="n">
-        <v>0.4056680964304741</v>
+        <v>0.3886072370702019</v>
       </c>
       <c r="E62" t="n">
-        <v>0.08912195297871497</v>
+        <v>0.02792187152984512</v>
       </c>
       <c r="F62" t="n">
-        <v>0.01364676752295124</v>
+        <v>0.01312743426878527</v>
       </c>
       <c r="G62" t="n">
         <v>0.02337681764920436</v>
       </c>
       <c r="H62" t="n">
-        <v>0.05489035078421119</v>
+        <v>0.05489035078421121</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3918900406318399</v>
+        <v>0.3388171704219033</v>
       </c>
       <c r="J62" t="n">
         <v>0.4899889565139167</v>
       </c>
       <c r="K62" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L62" t="n">
-        <v>0.2258064516129032</v>
+        <v>0.1935483870967742</v>
       </c>
       <c r="M62" t="n">
         <v>57</v>
@@ -5886,43 +5886,43 @@
         <v>0.09677419354838709</v>
       </c>
       <c r="O62" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="P62" t="n">
-        <v>0.5967741935483871</v>
+        <v>0.5483870967741935</v>
       </c>
       <c r="Q62" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="R62" t="n">
-        <v>0.3064516129032258</v>
+        <v>0.1935483870967742</v>
       </c>
       <c r="S62" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="T62" t="n">
-        <v>0.2096774193548387</v>
+        <v>0.1612903225806452</v>
       </c>
       <c r="U62" t="n">
-        <v>0.4570770776682223</v>
+        <v>0.4449838259858848</v>
       </c>
       <c r="V62" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W62" t="n">
-        <v>0.4938151248687246</v>
+        <v>0.5001540905059367</v>
       </c>
       <c r="X62" t="n">
         <v>8</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.4426311541674959</v>
+        <v>0.452471774707192</v>
       </c>
       <c r="Z62" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA62" t="n">
-        <v>0.4317256526909123</v>
+        <v>0.4449833794839311</v>
       </c>
       <c r="AB62" t="n">
         <v>9</v>
@@ -5935,28 +5935,28 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.04975816904726126</v>
+        <v>0.04735704308227625</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1083539928625279</v>
+        <v>0.1083054422205096</v>
       </c>
       <c r="D63" t="n">
-        <v>0.4130919860085082</v>
+        <v>0.3950837600064986</v>
       </c>
       <c r="E63" t="n">
-        <v>0.118068915926456</v>
+        <v>0.0562444562596548</v>
       </c>
       <c r="F63" t="n">
-        <v>0.04264278357671934</v>
+        <v>0.04132715199221412</v>
       </c>
       <c r="G63" t="n">
-        <v>0.04497014249802565</v>
+        <v>0.04497014249802566</v>
       </c>
       <c r="H63" t="n">
         <v>0.07616463515891099</v>
       </c>
       <c r="I63" t="n">
-        <v>0.3943117148931226</v>
+        <v>0.3413785287620172</v>
       </c>
       <c r="J63" t="n">
         <v>0.5262538759637436</v>
@@ -5968,49 +5968,49 @@
         <v>0.4516129032258064</v>
       </c>
       <c r="M63" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N63" t="n">
-        <v>0.3225806451612903</v>
+        <v>0.3064516129032258</v>
       </c>
       <c r="O63" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P63" t="n">
-        <v>0.6612903225806451</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="Q63" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="R63" t="n">
-        <v>0.5</v>
+        <v>0.4193548387096774</v>
       </c>
       <c r="S63" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T63" t="n">
-        <v>0.4354838709677419</v>
+        <v>0.4193548387096774</v>
       </c>
       <c r="U63" t="n">
-        <v>0.3882176841884978</v>
+        <v>0.3794793146420848</v>
       </c>
       <c r="V63" t="n">
         <v>16</v>
       </c>
       <c r="W63" t="n">
-        <v>0.3758289054678851</v>
+        <v>0.3806585575383375</v>
       </c>
       <c r="X63" t="n">
         <v>17</v>
       </c>
       <c r="Y63" t="n">
-        <v>0.3950115630162632</v>
+        <v>0.3849793761531596</v>
       </c>
       <c r="Z63" t="n">
         <v>17</v>
       </c>
       <c r="AA63" t="n">
-        <v>0.3540878557213085</v>
+        <v>0.358135792404982</v>
       </c>
       <c r="AB63" t="n">
         <v>16</v>
@@ -6049,7 +6049,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3004732800350395</v>
+        <v>0.298716614392491</v>
       </c>
       <c r="C2" t="n">
         <v>0.1436193929023161</v>
@@ -6062,7 +6062,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3649341169252127</v>
+        <v>0.362800592024358</v>
       </c>
       <c r="C3" t="n">
         <v>0.2390517592899662</v>
@@ -6075,10 +6075,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03298117046661134</v>
+        <v>0.03278835169416352</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1247836705740177</v>
+        <v>0.114585741396781</v>
       </c>
     </row>
     <row r="5">
@@ -6088,7 +6088,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01671347898575595</v>
+        <v>0.01661576648932929</v>
       </c>
       <c r="C5" t="n">
         <v>0.01094824071003378</v>
@@ -6101,7 +6101,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2225641628251474</v>
+        <v>0.2212629795117695</v>
       </c>
       <c r="C6" t="n">
         <v>0.1063806070976839</v>
@@ -6114,10 +6114,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03309552513565491</v>
+        <v>0.03874836678075101</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1252163294259823</v>
+        <v>0.135414258603219</v>
       </c>
     </row>
     <row r="8">
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02923826562657815</v>
+        <v>0.02906732910713769</v>
       </c>
       <c r="C8" t="n">
         <v>0.25</v>
@@ -6171,13 +6171,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4752242026162366</v>
+        <v>0.4744621909695046</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2053942451071088</v>
+        <v>0.3118599205521344</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.340620349038665</v>
+        <v>-0.2267790926663584</v>
       </c>
     </row>
     <row r="3">
@@ -6187,13 +6187,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5116517008237824</v>
+        <v>0.522754121532087</v>
       </c>
       <c r="C3" t="n">
-        <v>0.184131638437099</v>
+        <v>0.07318173971459471</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1220610377402451</v>
+        <v>0.1614041518649291</v>
       </c>
     </row>
     <row r="4">
@@ -6203,13 +6203,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.2514535427346625</v>
+        <v>-0.2234115551717578</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6397082391087059</v>
+        <v>0.4228951943796183</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1648004994031726</v>
+        <v>0.5217940076476613</v>
       </c>
     </row>
     <row r="5">
@@ -6219,13 +6219,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2459447157236481</v>
+        <v>0.2500328626530264</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2040889644267659</v>
+        <v>0.06023319715467084</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4723861032934999</v>
+        <v>0.5147548826256257</v>
       </c>
     </row>
     <row r="6">
@@ -6235,13 +6235,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4163035901402223</v>
+        <v>0.4097524126037182</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3142305396534276</v>
+        <v>0.497550253133396</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4429954744080764</v>
+        <v>-0.2498531723633461</v>
       </c>
     </row>
     <row r="7">
@@ -6251,13 +6251,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3362890119819237</v>
+        <v>0.3284244033169473</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.6114700783975971</v>
+        <v>-0.5875362650356185</v>
       </c>
       <c r="D7" t="n">
-        <v>0.003684568378236911</v>
+        <v>-0.1999128437605099</v>
       </c>
     </row>
     <row r="8">
@@ -6267,13 +6267,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3197777794066963</v>
+        <v>0.3367862438435426</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.0198322563656224</v>
+        <v>-0.3495201315111942</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6500095993968317</v>
+        <v>0.5318708625651674</v>
       </c>
     </row>
   </sheetData>
